--- a/scripts/data/50m_Masculino_Absoluto_Libre.xlsx
+++ b/scripts/data/50m_Masculino_Absoluto_Libre.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O168"/>
+  <dimension ref="A1:O171"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1115,22 +1115,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C17" t="str">
-        <v>ARTUR SAIENKO</v>
+        <v>CESAR ARROYO PEREZ</v>
       </c>
       <c r="D17">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="E17" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F17" t="str">
-        <v>00:00:27.90</v>
+        <v>00:00:27.84</v>
       </c>
       <c r="G17">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="H17" s="1">
-        <v>45815.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I17" t="str">
         <v>Deportista</v>
@@ -1142,10 +1142,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L17" t="str">
-        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M17" t="str">
-        <v>Castellón</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N17" t="str">
         <v>No</v>
@@ -1159,22 +1159,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C18" t="str">
-        <v>PABLO SERRANO MARCOS</v>
+        <v>ARTUR SAIENKO</v>
       </c>
       <c r="D18">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="E18" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F18" t="str">
-        <v>00:00:27.99</v>
+        <v>00:00:27.90</v>
       </c>
       <c r="G18">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H18" s="1">
-        <v>44723.99949074074</v>
+        <v>45815.99949074074</v>
       </c>
       <c r="I18" t="str">
         <v>Deportista</v>
@@ -1186,10 +1186,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L18" t="str">
-        <v>X TROFEO REAL CLUB NATACIÓN DELFÍN</v>
+        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M18" t="str">
-        <v>Sedavi</v>
+        <v>Castellón</v>
       </c>
       <c r="N18" t="str">
         <v>No</v>
@@ -1203,10 +1203,10 @@
         <v>50 Libre</v>
       </c>
       <c r="C19" t="str">
-        <v>JUAN CAMACHO MARTINEZ</v>
+        <v>PABLO SERRANO MARCOS</v>
       </c>
       <c r="D19">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="E19" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
@@ -1218,7 +1218,7 @@
         <v>417</v>
       </c>
       <c r="H19" s="1">
-        <v>45816.99949074074</v>
+        <v>44723.99949074074</v>
       </c>
       <c r="I19" t="str">
         <v>Deportista</v>
@@ -1230,13 +1230,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L19" t="str">
-        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>X TROFEO REAL CLUB NATACIÓN DELFÍN</v>
       </c>
       <c r="M19" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N19" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="20">
@@ -1247,22 +1247,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C20" t="str">
-        <v>ONOFRE BONDIA VELERT</v>
+        <v>JUAN CAMACHO MARTINEZ</v>
       </c>
       <c r="D20">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="E20" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F20" t="str">
-        <v>00:00:28.03</v>
+        <v>00:00:27.99</v>
       </c>
       <c r="G20">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H20" s="1">
-        <v>44576.99949074074</v>
+        <v>45816.99949074074</v>
       </c>
       <c r="I20" t="str">
         <v>Deportista</v>
@@ -1274,13 +1274,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L20" t="str">
-        <v>Autonomico Infantil de Invierno</v>
+        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M20" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N20" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="21">
@@ -1291,22 +1291,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C21" t="str">
-        <v>CESAR ARROYO PEREZ</v>
+        <v>ONOFRE BONDIA VELERT</v>
       </c>
       <c r="D21">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="E21" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F21" t="str">
-        <v>00:00:28.17</v>
+        <v>00:00:28.03</v>
       </c>
       <c r="G21">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="H21" s="1">
-        <v>46081.99949074074</v>
+        <v>44576.99949074074</v>
       </c>
       <c r="I21" t="str">
         <v>Deportista</v>
@@ -1318,10 +1318,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L21" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>Autonomico Infantil de Invierno</v>
       </c>
       <c r="M21" t="str">
-        <v>CASTELLÓN</v>
+        <v>Elche</v>
       </c>
       <c r="N21" t="str">
         <v>No</v>
@@ -1907,22 +1907,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C35" t="str">
-        <v>GEORGI ZHELYAZKOV</v>
+        <v>HUGO RODRIGUEZ GARCIA</v>
       </c>
       <c r="D35">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E35" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F35" t="str">
-        <v>00:00:29.57</v>
+        <v>00:00:29.45</v>
       </c>
       <c r="G35">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H35" s="1">
-        <v>45710.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I35" t="str">
         <v>Deportista</v>
@@ -1934,10 +1934,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L35" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M35" t="str">
-        <v>ELCHE</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N35" t="str">
         <v>No</v>
@@ -1951,22 +1951,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C36" t="str">
-        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
+        <v>GEORGI ZHELYAZKOV</v>
       </c>
       <c r="D36">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="E36" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F36" t="str">
-        <v>00:00:29.66</v>
+        <v>00:00:29.57</v>
       </c>
       <c r="G36">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H36" s="1">
-        <v>42903.99949074074</v>
+        <v>45710.99949074074</v>
       </c>
       <c r="I36" t="str">
         <v>Deportista</v>
@@ -1978,10 +1978,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L36" t="str">
-        <v>VI TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M36" t="str">
-        <v>PARQUE OESTE</v>
+        <v>ELCHE</v>
       </c>
       <c r="N36" t="str">
         <v>No</v>
@@ -1995,22 +1995,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C37" t="str">
-        <v>TEIMUR SULEIMANOV</v>
+        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
       </c>
       <c r="D37">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="E37" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F37" t="str">
-        <v>00:00:29.69</v>
+        <v>00:00:29.66</v>
       </c>
       <c r="G37">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H37" s="1">
-        <v>44723.99949074074</v>
+        <v>42903.99949074074</v>
       </c>
       <c r="I37" t="str">
         <v>Deportista</v>
@@ -2022,10 +2022,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L37" t="str">
-        <v>X TROFEO REAL CLUB NATACIÓN DELFÍN</v>
+        <v>VI TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M37" t="str">
-        <v>Sedavi</v>
+        <v>PARQUE OESTE</v>
       </c>
       <c r="N37" t="str">
         <v>No</v>
@@ -2039,22 +2039,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C38" t="str">
-        <v>KYRYLO KUZMIN</v>
+        <v>TEIMUR SULEIMANOV</v>
       </c>
       <c r="D38">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="E38" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F38" t="str">
-        <v>00:00:29.86</v>
+        <v>00:00:29.69</v>
       </c>
       <c r="G38">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="H38" s="1">
-        <v>45472.99949074074</v>
+        <v>44723.99949074074</v>
       </c>
       <c r="I38" t="str">
         <v>Deportista</v>
@@ -2066,10 +2066,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L38" t="str">
-        <v>Autonomico Infantil de Verano</v>
+        <v>X TROFEO REAL CLUB NATACIÓN DELFÍN</v>
       </c>
       <c r="M38" t="str">
-        <v>Sedavi(Valencia)</v>
+        <v>Sedavi</v>
       </c>
       <c r="N38" t="str">
         <v>No</v>
@@ -2083,22 +2083,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C39" t="str">
-        <v>FELIPE SEBASTIAN HERMIDA BATTISTON</v>
+        <v>KYRYLO KUZMIN</v>
       </c>
       <c r="D39">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="E39" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F39" t="str">
-        <v>00:00:29.88</v>
+        <v>00:00:29.86</v>
       </c>
       <c r="G39">
         <v>343</v>
       </c>
       <c r="H39" s="1">
-        <v>46171.99949074074</v>
+        <v>45472.99949074074</v>
       </c>
       <c r="I39" t="str">
         <v>Deportista</v>
@@ -2107,13 +2107,13 @@
         <v>50m</v>
       </c>
       <c r="K39" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L39" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>Autonomico Infantil de Verano</v>
       </c>
       <c r="M39" t="str">
-        <v>Vila-Real</v>
+        <v>Sedavi(Valencia)</v>
       </c>
       <c r="N39" t="str">
         <v>No</v>
@@ -2127,22 +2127,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C40" t="str">
-        <v>SIMON MORENO RODRIGUEZ</v>
+        <v>FELIPE SEBASTIAN HERMIDA BATTISTON</v>
       </c>
       <c r="D40">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E40" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F40" t="str">
-        <v>00:00:30.08</v>
+        <v>00:00:29.88</v>
       </c>
       <c r="G40">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="H40" s="1">
-        <v>45836.99949074074</v>
+        <v>46171.99949074074</v>
       </c>
       <c r="I40" t="str">
         <v>Deportista</v>
@@ -2151,13 +2151,13 @@
         <v>50m</v>
       </c>
       <c r="K40" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L40" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M40" t="str">
-        <v>Castellón</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N40" t="str">
         <v>No</v>
@@ -2180,13 +2180,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F41" t="str">
-        <v>00:00:30.11</v>
+        <v>00:00:30.05</v>
       </c>
       <c r="G41">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H41" s="1">
-        <v>46081.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I41" t="str">
         <v>Deportista</v>
@@ -2198,10 +2198,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L41" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M41" t="str">
-        <v>CASTELLÓN</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N41" t="str">
         <v>No</v>
@@ -2215,7 +2215,7 @@
         <v>50 Libre</v>
       </c>
       <c r="C42" t="str">
-        <v>FEDERICO MANUEL HERMIDA BATTISTON</v>
+        <v>SIMON MORENO RODRIGUEZ</v>
       </c>
       <c r="D42">
         <v>2010</v>
@@ -2224,10 +2224,10 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F42" t="str">
-        <v>00:00:30.25</v>
+        <v>00:00:30.08</v>
       </c>
       <c r="G42">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="H42" s="1">
         <v>45836.99949074074</v>
@@ -2259,22 +2259,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C43" t="str">
-        <v>DAVID MUÑOZ CEBOLLA</v>
+        <v>FEDERICO MANUEL HERMIDA BATTISTON</v>
       </c>
       <c r="D43">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E43" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F43" t="str">
-        <v>00:00:30.39</v>
+        <v>00:00:30.25</v>
       </c>
       <c r="G43">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H43" s="1">
-        <v>45347.99949074074</v>
+        <v>45836.99949074074</v>
       </c>
       <c r="I43" t="str">
         <v>Deportista</v>
@@ -2286,13 +2286,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L43" t="str">
-        <v>Autonomico Infantil de Invierno 2024</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
       </c>
       <c r="M43" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N43" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="44">
@@ -2303,22 +2303,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C44" t="str">
-        <v>RAUL PEREZ PEIRATS</v>
+        <v>DAVID MUÑOZ CEBOLLA</v>
       </c>
       <c r="D44">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="E44" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F44" t="str">
-        <v>00:00:30.85</v>
+        <v>00:00:30.39</v>
       </c>
       <c r="G44">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="H44" s="1">
-        <v>44359.99949074074</v>
+        <v>45347.99949074074</v>
       </c>
       <c r="I44" t="str">
         <v>Deportista</v>
@@ -2330,10 +2330,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L44" t="str">
-        <v>IX Trofeo Real Club Natación Delfín</v>
+        <v>Autonomico Infantil de Invierno 2024</v>
       </c>
       <c r="M44" t="str">
-        <v>Sedavi</v>
+        <v>Elche</v>
       </c>
       <c r="N44" t="str">
         <v>Sí</v>
@@ -2347,22 +2347,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C45" t="str">
-        <v>GEORGI ZHELYAZKOV</v>
+        <v>RAUL PEREZ PEIRATS</v>
       </c>
       <c r="D45">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="E45" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F45" t="str">
-        <v>00:00:31.12</v>
+        <v>00:00:30.85</v>
       </c>
       <c r="G45">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="H45" s="1">
-        <v>45472.99949074074</v>
+        <v>44359.99949074074</v>
       </c>
       <c r="I45" t="str">
         <v>Deportista</v>
@@ -2374,13 +2374,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L45" t="str">
-        <v>Autonomico Infantil de Verano</v>
+        <v>IX Trofeo Real Club Natación Delfín</v>
       </c>
       <c r="M45" t="str">
-        <v>Sedavi(Valencia)</v>
+        <v>Sedavi</v>
       </c>
       <c r="N45" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="46">
@@ -2391,7 +2391,7 @@
         <v>50 Libre</v>
       </c>
       <c r="C46" t="str">
-        <v>HUGO RODRIGUEZ GARCIA</v>
+        <v>MARCOS PEDRERO MARTINEZ</v>
       </c>
       <c r="D46">
         <v>2012</v>
@@ -2400,13 +2400,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F46" t="str">
-        <v>00:00:31.16</v>
+        <v>00:00:30.99</v>
       </c>
       <c r="G46">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H46" s="1">
-        <v>46081.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I46" t="str">
         <v>Deportista</v>
@@ -2418,10 +2418,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L46" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M46" t="str">
-        <v>CASTELLÓN</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N46" t="str">
         <v>No</v>
@@ -2435,22 +2435,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C47" t="str">
-        <v>MARCOS PEDRERO MARTINEZ</v>
+        <v>GEORGI ZHELYAZKOV</v>
       </c>
       <c r="D47">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E47" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F47" t="str">
-        <v>00:00:31.40</v>
+        <v>00:00:31.12</v>
       </c>
       <c r="G47">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="H47" s="1">
-        <v>46081.99949074074</v>
+        <v>45472.99949074074</v>
       </c>
       <c r="I47" t="str">
         <v>Deportista</v>
@@ -2462,10 +2462,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L47" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>Autonomico Infantil de Verano</v>
       </c>
       <c r="M47" t="str">
-        <v>CASTELLÓN</v>
+        <v>Sedavi(Valencia)</v>
       </c>
       <c r="N47" t="str">
         <v>No</v>
@@ -2523,22 +2523,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C49" t="str">
-        <v>MANEL LAZARO VILANOVA</v>
+        <v>ILIYAN ILIYANOV KIRYAKOV</v>
       </c>
       <c r="D49">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="E49" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F49" t="str">
-        <v>00:00:31.69</v>
+        <v>00:00:31.52</v>
       </c>
       <c r="G49">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H49" s="1">
-        <v>44709.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I49" t="str">
         <v>Deportista</v>
@@ -2547,13 +2547,13 @@
         <v>50m</v>
       </c>
       <c r="K49" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L49" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M49" t="str">
-        <v>Sedavi</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N49" t="str">
         <v>No</v>
@@ -2567,22 +2567,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C50" t="str">
-        <v>JORDI SOLERA PAREDES</v>
+        <v>MANEL LAZARO VILANOVA</v>
       </c>
       <c r="D50">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="E50" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F50" t="str">
-        <v>00:00:31.83</v>
+        <v>00:00:31.69</v>
       </c>
       <c r="G50">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H50" s="1">
-        <v>45801.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I50" t="str">
         <v>Deportista</v>
@@ -2591,16 +2591,16 @@
         <v>50m</v>
       </c>
       <c r="K50" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L50" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M50" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N50" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="51">
@@ -2611,22 +2611,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C51" t="str">
-        <v>VICENTE SILLA TAMARIT</v>
+        <v>JORDI SOLERA PAREDES</v>
       </c>
       <c r="D51">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E51" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F51" t="str">
-        <v>00:00:32.22</v>
+        <v>00:00:31.83</v>
       </c>
       <c r="G51">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="H51" s="1">
-        <v>45710.99949074074</v>
+        <v>45801.99949074074</v>
       </c>
       <c r="I51" t="str">
         <v>Deportista</v>
@@ -2638,13 +2638,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L51" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M51" t="str">
-        <v>ELCHE</v>
+        <v>Castellón</v>
       </c>
       <c r="N51" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="52">
@@ -2655,22 +2655,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C52" t="str">
-        <v>ROGER MASCARELL CARRILLO DE ALBORNOZ</v>
+        <v>VICENTE SILLA TAMARIT</v>
       </c>
       <c r="D52">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E52" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F52" t="str">
-        <v>00:00:32.26</v>
+        <v>00:00:32.22</v>
       </c>
       <c r="G52">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H52" s="1">
-        <v>46171.99949074074</v>
+        <v>45710.99949074074</v>
       </c>
       <c r="I52" t="str">
         <v>Deportista</v>
@@ -2679,13 +2679,13 @@
         <v>50m</v>
       </c>
       <c r="K52" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L52" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M52" t="str">
-        <v>Vila-Real</v>
+        <v>ELCHE</v>
       </c>
       <c r="N52" t="str">
         <v>No</v>
@@ -2699,22 +2699,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C53" t="str">
-        <v>RAUL VILA ALMAZORA</v>
+        <v>ROGER MASCARELL CARRILLO DE ALBORNOZ</v>
       </c>
       <c r="D53">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="E53" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F53" t="str">
-        <v>00:00:32.29</v>
+        <v>00:00:32.26</v>
       </c>
       <c r="G53">
         <v>272</v>
       </c>
       <c r="H53" s="1">
-        <v>43638.99949074074</v>
+        <v>46171.99949074074</v>
       </c>
       <c r="I53" t="str">
         <v>Deportista</v>
@@ -2726,10 +2726,10 @@
         <v>Manual</v>
       </c>
       <c r="L53" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M53" t="str">
-        <v>Moncada</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N53" t="str">
         <v>No</v>
@@ -2743,22 +2743,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C54" t="str">
-        <v>IKER BARTOLIN GIMENEZ</v>
+        <v>RAUL VILA ALMAZORA</v>
       </c>
       <c r="D54">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="E54" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F54" t="str">
-        <v>00:00:32.32</v>
+        <v>00:00:32.29</v>
       </c>
       <c r="G54">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H54" s="1">
-        <v>46046.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I54" t="str">
         <v>Deportista</v>
@@ -2767,16 +2767,16 @@
         <v>50m</v>
       </c>
       <c r="K54" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L54" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M54" t="str">
-        <v>Elche</v>
+        <v>Moncada</v>
       </c>
       <c r="N54" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="55">
@@ -2787,22 +2787,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C55" t="str">
-        <v>MARCOS RODRIGUEZ SERVER</v>
+        <v>IKER BARTOLIN GIMENEZ</v>
       </c>
       <c r="D55">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E55" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F55" t="str">
-        <v>00:00:32.37</v>
+        <v>00:00:32.32</v>
       </c>
       <c r="G55">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H55" s="1">
-        <v>45836.99949074074</v>
+        <v>46046.99949074074</v>
       </c>
       <c r="I55" t="str">
         <v>Deportista</v>
@@ -2814,13 +2814,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L55" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M55" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N55" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="56">
@@ -2831,22 +2831,22 @@
         <v>50 Libre</v>
       </c>
       <c r="C56" t="str">
-        <v>DANIEL DIAZ GONZALEZ</v>
+        <v>MARCOS RODRIGUEZ SERVER</v>
       </c>
       <c r="D56">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E56" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F56" t="str">
-        <v>00:00:32.45</v>
+        <v>00:00:32.37</v>
       </c>
       <c r="G56">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H56" s="1">
-        <v>46171.99949074074</v>
+        <v>45836.99949074074</v>
       </c>
       <c r="I56" t="str">
         <v>Deportista</v>
@@ -2855,13 +2855,13 @@
         <v>50m</v>
       </c>
       <c r="K56" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L56" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
       </c>
       <c r="M56" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N56" t="str">
         <v>No</v>
@@ -2869,28 +2869,28 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>100 Libre</v>
+        <v>50 Libre</v>
       </c>
       <c r="C57" t="str">
-        <v>DAVID SIENRA BUGS</v>
+        <v>DANIEL DIAZ GONZALEZ</v>
       </c>
       <c r="D57">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="E57" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F57" t="str">
-        <v>00:00:55.75</v>
+        <v>00:00:32.45</v>
       </c>
       <c r="G57">
-        <v>577</v>
+        <v>268</v>
       </c>
       <c r="H57" s="1">
-        <v>45494.99949074074</v>
+        <v>46171.99949074074</v>
       </c>
       <c r="I57" t="str">
         <v>Deportista</v>
@@ -2899,13 +2899,13 @@
         <v>50m</v>
       </c>
       <c r="K57" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L57" t="str">
-        <v>Campeonato Autonómico Open Junior Y Absoluto de Verano</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M57" t="str">
-        <v>Castellón</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N57" t="str">
         <v>No</v>
@@ -2913,28 +2913,28 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B58" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C58" t="str">
-        <v>TYMOFII VLASENKO</v>
+        <v>DAVID SIENRA BUGS</v>
       </c>
       <c r="D58">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="E58" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F58" t="str">
-        <v>00:00:56.26</v>
+        <v>00:00:55.75</v>
       </c>
       <c r="G58">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="H58" s="1">
-        <v>45095.99949074074</v>
+        <v>45494.99949074074</v>
       </c>
       <c r="I58" t="str">
         <v>Deportista</v>
@@ -2946,7 +2946,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L58" t="str">
-        <v>I Trofeo Federación 226ERS piscina 50m</v>
+        <v>Campeonato Autonómico Open Junior Y Absoluto de Verano</v>
       </c>
       <c r="M58" t="str">
         <v>Castellón</v>
@@ -2957,28 +2957,28 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B59" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C59" t="str">
-        <v>ENRIQUE GALLIFA TRONCH</v>
+        <v>TYMOFII VLASENKO</v>
       </c>
       <c r="D59">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="E59" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F59" t="str">
-        <v>00:00:57.14</v>
+        <v>00:00:56.26</v>
       </c>
       <c r="G59">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="H59" s="1">
-        <v>45801.99949074074</v>
+        <v>45095.99949074074</v>
       </c>
       <c r="I59" t="str">
         <v>Deportista</v>
@@ -2990,39 +2990,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L59" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>I Trofeo Federación 226ERS piscina 50m</v>
       </c>
       <c r="M59" t="str">
         <v>Castellón</v>
       </c>
       <c r="N59" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B60" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C60" t="str">
-        <v>DAVID HERREROS COLL</v>
+        <v>ENRIQUE GALLIFA TRONCH</v>
       </c>
       <c r="D60">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="E60" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F60" t="str">
-        <v>00:00:57.52</v>
+        <v>00:00:57.14</v>
       </c>
       <c r="G60">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="H60" s="1">
-        <v>45696.99949074074</v>
+        <v>45801.99949074074</v>
       </c>
       <c r="I60" t="str">
         <v>Deportista</v>
@@ -3034,7 +3034,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L60" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2025 C.V.</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M60" t="str">
         <v>Castellón</v>
@@ -3045,28 +3045,28 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B61" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C61" t="str">
-        <v>MIGUEL BAIXAULI MUÑOZ</v>
+        <v>DAVID HERREROS COLL</v>
       </c>
       <c r="D61">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="E61" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F61" t="str">
-        <v>00:00:57.77</v>
+        <v>00:00:57.52</v>
       </c>
       <c r="G61">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H61" s="1">
-        <v>44632.99949074074</v>
+        <v>45696.99949074074</v>
       </c>
       <c r="I61" t="str">
         <v>Deportista</v>
@@ -3078,39 +3078,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L61" t="str">
-        <v>Campeonato Autonómico de Invierno Jr-Abs OPEN P50</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M61" t="str">
-        <v>Castellon</v>
+        <v>Castellón</v>
       </c>
       <c r="N61" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B62" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C62" t="str">
-        <v>JAUME MORENO ROMERO</v>
+        <v>MIGUEL BAIXAULI MUÑOZ</v>
       </c>
       <c r="D62">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="E62" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F62" t="str">
-        <v>00:00:57.78</v>
+        <v>00:00:57.77</v>
       </c>
       <c r="G62">
         <v>518</v>
       </c>
       <c r="H62" s="1">
-        <v>46075.99949074074</v>
+        <v>44632.99949074074</v>
       </c>
       <c r="I62" t="str">
         <v>Deportista</v>
@@ -3122,10 +3122,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L62" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
+        <v>Campeonato Autonómico de Invierno Jr-Abs OPEN P50</v>
       </c>
       <c r="M62" t="str">
-        <v>Elche</v>
+        <v>Castellon</v>
       </c>
       <c r="N62" t="str">
         <v>No</v>
@@ -3133,28 +3133,28 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B63" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C63" t="str">
-        <v>ALVARO TERUEL BELLOCH</v>
+        <v>JAUME MORENO ROMERO</v>
       </c>
       <c r="D63">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E63" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F63" t="str">
-        <v>00:00:58.16</v>
+        <v>00:00:57.78</v>
       </c>
       <c r="G63">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="H63" s="1">
-        <v>46047.99949074074</v>
+        <v>46075.99949074074</v>
       </c>
       <c r="I63" t="str">
         <v>Deportista</v>
@@ -3166,7 +3166,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L63" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
       </c>
       <c r="M63" t="str">
         <v>Elche</v>
@@ -3177,28 +3177,28 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B64" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C64" t="str">
-        <v>ALEJANDRO FABIA NOGUERA</v>
+        <v>ALVARO TERUEL BELLOCH</v>
       </c>
       <c r="D64">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="E64" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F64" t="str">
-        <v>00:00:58.59</v>
+        <v>00:00:58.16</v>
       </c>
       <c r="G64">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="H64" s="1">
-        <v>46173.99949074074</v>
+        <v>46047.99949074074</v>
       </c>
       <c r="I64" t="str">
         <v>Deportista</v>
@@ -3207,13 +3207,13 @@
         <v>50m</v>
       </c>
       <c r="K64" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L64" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M64" t="str">
-        <v>Vila-Real</v>
+        <v>Elche</v>
       </c>
       <c r="N64" t="str">
         <v>No</v>
@@ -3221,28 +3221,28 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B65" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C65" t="str">
-        <v>NEIZAN DE LUCA RUBIO</v>
+        <v>ALEJANDRO FABIA NOGUERA</v>
       </c>
       <c r="D65">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E65" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F65" t="str">
-        <v>00:00:59.35</v>
+        <v>00:00:58.59</v>
       </c>
       <c r="G65">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H65" s="1">
-        <v>46082.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I65" t="str">
         <v>Deportista</v>
@@ -3251,13 +3251,13 @@
         <v>50m</v>
       </c>
       <c r="K65" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L65" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M65" t="str">
-        <v>CASTELLÓN</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N65" t="str">
         <v>No</v>
@@ -3265,28 +3265,28 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B66" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C66" t="str">
-        <v>MARTIN FABIA NOGUERA</v>
+        <v>NEIZAN DE LUCA RUBIO</v>
       </c>
       <c r="D66">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="E66" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F66" t="str">
-        <v>00:00:59.94</v>
+        <v>00:00:59.35</v>
       </c>
       <c r="G66">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="H66" s="1">
-        <v>45108.99949074074</v>
+        <v>46082.99949074074</v>
       </c>
       <c r="I66" t="str">
         <v>Deportista</v>
@@ -3298,10 +3298,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L66" t="str">
-        <v>Campeonato Autonomico Infantil de Verano</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
       </c>
       <c r="M66" t="str">
-        <v>ELDA</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N66" t="str">
         <v>No</v>
@@ -3309,28 +3309,28 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B67" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C67" t="str">
-        <v>DANIEL FERNANDEZ CARO</v>
+        <v>MARTIN FABIA NOGUERA</v>
       </c>
       <c r="D67">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="E67" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F67" t="str">
-        <v>00:01:00.00</v>
+        <v>00:00:59.94</v>
       </c>
       <c r="G67">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H67" s="1">
-        <v>46173.99949074074</v>
+        <v>45108.99949074074</v>
       </c>
       <c r="I67" t="str">
         <v>Deportista</v>
@@ -3339,13 +3339,13 @@
         <v>50m</v>
       </c>
       <c r="K67" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L67" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>Campeonato Autonomico Infantil de Verano</v>
       </c>
       <c r="M67" t="str">
-        <v>Vila-Real</v>
+        <v>ELDA</v>
       </c>
       <c r="N67" t="str">
         <v>No</v>
@@ -3353,28 +3353,28 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C68" t="str">
-        <v>CARLOS MENDEZ SALVADOR</v>
+        <v>DANIEL FERNANDEZ CARO</v>
       </c>
       <c r="D68">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="E68" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F68" t="str">
-        <v>00:01:00.06</v>
+        <v>00:01:00.00</v>
       </c>
       <c r="G68">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H68" s="1">
-        <v>46075.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I68" t="str">
         <v>Deportista</v>
@@ -3383,27 +3383,27 @@
         <v>50m</v>
       </c>
       <c r="K68" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L68" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M68" t="str">
-        <v>Elche</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N68" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B69" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C69" t="str">
-        <v>JUAN CAMACHO MARTINEZ</v>
+        <v>CARLOS MENDEZ SALVADOR</v>
       </c>
       <c r="D69">
         <v>2010</v>
@@ -3412,13 +3412,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F69" t="str">
-        <v>00:01:00.15</v>
+        <v>00:01:00.06</v>
       </c>
       <c r="G69">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H69" s="1">
-        <v>45816.99949074074</v>
+        <v>46075.99949074074</v>
       </c>
       <c r="I69" t="str">
         <v>Deportista</v>
@@ -3430,39 +3430,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L69" t="str">
-        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
       </c>
       <c r="M69" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N69" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B70" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C70" t="str">
-        <v>ONOFRE BONDIA VELERT</v>
+        <v>JUAN CAMACHO MARTINEZ</v>
       </c>
       <c r="D70">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="E70" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F70" t="str">
-        <v>00:01:01.05</v>
+        <v>00:01:00.15</v>
       </c>
       <c r="G70">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="H70" s="1">
-        <v>44577.99949074074</v>
+        <v>45816.99949074074</v>
       </c>
       <c r="I70" t="str">
         <v>Deportista</v>
@@ -3474,10 +3474,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L70" t="str">
-        <v>Autonomico Infantil de Invierno</v>
+        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M70" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N70" t="str">
         <v>No</v>
@@ -3485,28 +3485,28 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B71" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C71" t="str">
-        <v>PABLO SERRANO MARCOS</v>
+        <v>ONOFRE BONDIA VELERT</v>
       </c>
       <c r="D71">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="E71" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F71" t="str">
-        <v>00:01:02.15</v>
+        <v>00:01:01.05</v>
       </c>
       <c r="G71">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="H71" s="1">
-        <v>44723.99949074074</v>
+        <v>44577.99949074074</v>
       </c>
       <c r="I71" t="str">
         <v>Deportista</v>
@@ -3518,10 +3518,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L71" t="str">
-        <v>X TROFEO REAL CLUB NATACIÓN DELFÍN</v>
+        <v>Autonomico Infantil de Invierno</v>
       </c>
       <c r="M71" t="str">
-        <v>Sedavi</v>
+        <v>Elche</v>
       </c>
       <c r="N71" t="str">
         <v>No</v>
@@ -3529,28 +3529,28 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B72" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C72" t="str">
-        <v>FLAVIUS MUSCALU</v>
+        <v>CESAR ARROYO PEREZ</v>
       </c>
       <c r="D72">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="E72" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F72" t="str">
-        <v>00:01:02.56</v>
+        <v>00:01:01.86</v>
       </c>
       <c r="G72">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="H72" s="1">
-        <v>44976.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I72" t="str">
         <v>Deportista</v>
@@ -3562,10 +3562,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L72" t="str">
-        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M72" t="str">
-        <v>Elche</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N72" t="str">
         <v>No</v>
@@ -3573,28 +3573,28 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B73" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C73" t="str">
-        <v>ADAM AMZIL IJRRARE</v>
+        <v>PABLO SERRANO MARCOS</v>
       </c>
       <c r="D73">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="E73" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F73" t="str">
-        <v>00:01:02.73</v>
+        <v>00:01:02.15</v>
       </c>
       <c r="G73">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="H73" s="1">
-        <v>46173.99949074074</v>
+        <v>44723.99949074074</v>
       </c>
       <c r="I73" t="str">
         <v>Deportista</v>
@@ -3603,13 +3603,13 @@
         <v>50m</v>
       </c>
       <c r="K73" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L73" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>X TROFEO REAL CLUB NATACIÓN DELFÍN</v>
       </c>
       <c r="M73" t="str">
-        <v>Vila-Real</v>
+        <v>Sedavi</v>
       </c>
       <c r="N73" t="str">
         <v>No</v>
@@ -3617,13 +3617,13 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B74" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C74" t="str">
-        <v>RAUL PEREZ PEIRATS</v>
+        <v>FLAVIUS MUSCALU</v>
       </c>
       <c r="D74">
         <v>2004</v>
@@ -3632,13 +3632,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F74" t="str">
-        <v>00:01:03.18</v>
+        <v>00:01:02.56</v>
       </c>
       <c r="G74">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="H74" s="1">
-        <v>44359.99949074074</v>
+        <v>44976.99949074074</v>
       </c>
       <c r="I74" t="str">
         <v>Deportista</v>
@@ -3650,10 +3650,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L74" t="str">
-        <v>IX Trofeo Real Club Natación Delfín</v>
+        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
       </c>
       <c r="M74" t="str">
-        <v>Sedavi</v>
+        <v>Elche</v>
       </c>
       <c r="N74" t="str">
         <v>No</v>
@@ -3661,28 +3661,28 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B75" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C75" t="str">
-        <v>CESAR ARROYO PEREZ</v>
+        <v>ADAM AMZIL IJRRARE</v>
       </c>
       <c r="D75">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="E75" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F75" t="str">
-        <v>00:01:03.30</v>
+        <v>00:01:02.73</v>
       </c>
       <c r="G75">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="H75" s="1">
-        <v>46082.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I75" t="str">
         <v>Deportista</v>
@@ -3691,13 +3691,13 @@
         <v>50m</v>
       </c>
       <c r="K75" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L75" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M75" t="str">
-        <v>CASTELLÓN</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N75" t="str">
         <v>No</v>
@@ -3705,28 +3705,28 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B76" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C76" t="str">
-        <v>DAVID ESCOBEDO IRUETA</v>
+        <v>RAUL PEREZ PEIRATS</v>
       </c>
       <c r="D76">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="E76" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F76" t="str">
-        <v>00:01:03.69</v>
+        <v>00:01:03.18</v>
       </c>
       <c r="G76">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="H76" s="1">
-        <v>44576.99949074074</v>
+        <v>44359.99949074074</v>
       </c>
       <c r="I76" t="str">
         <v>Deportista</v>
@@ -3738,10 +3738,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L76" t="str">
-        <v>Autonomico Infantil de Invierno</v>
+        <v>IX Trofeo Real Club Natación Delfín</v>
       </c>
       <c r="M76" t="str">
-        <v>Elche</v>
+        <v>Sedavi</v>
       </c>
       <c r="N76" t="str">
         <v>No</v>
@@ -3749,28 +3749,28 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B77" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C77" t="str">
-        <v>ARTUR SAIENKO</v>
+        <v>DAVID ESCOBEDO IRUETA</v>
       </c>
       <c r="D77">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="E77" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F77" t="str">
-        <v>00:01:03.87</v>
+        <v>00:01:03.69</v>
       </c>
       <c r="G77">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H77" s="1">
-        <v>45683.99949074074</v>
+        <v>44576.99949074074</v>
       </c>
       <c r="I77" t="str">
         <v>Deportista</v>
@@ -3782,7 +3782,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L77" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>Autonomico Infantil de Invierno</v>
       </c>
       <c r="M77" t="str">
         <v>Elche</v>
@@ -3793,28 +3793,28 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B78" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C78" t="str">
-        <v>GERMAN MALLO FAURE</v>
+        <v>ALEXIS GARCIA VALERO</v>
       </c>
       <c r="D78">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="E78" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F78" t="str">
-        <v>00:01:03.94</v>
+        <v>00:01:03.71</v>
       </c>
       <c r="G78">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H78" s="1">
-        <v>44976.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I78" t="str">
         <v>Deportista</v>
@@ -3826,10 +3826,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L78" t="str">
-        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M78" t="str">
-        <v>Elche</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N78" t="str">
         <v>No</v>
@@ -3837,28 +3837,28 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B79" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C79" t="str">
-        <v>GONZALO YUSTE TRUJILLO</v>
+        <v>ARTUR SAIENKO</v>
       </c>
       <c r="D79">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="E79" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F79" t="str">
-        <v>00:01:04.16</v>
+        <v>00:01:03.87</v>
       </c>
       <c r="G79">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H79" s="1">
-        <v>45711.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I79" t="str">
         <v>Deportista</v>
@@ -3870,10 +3870,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L79" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M79" t="str">
-        <v>ELCHE</v>
+        <v>Elche</v>
       </c>
       <c r="N79" t="str">
         <v>No</v>
@@ -3881,28 +3881,28 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B80" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C80" t="str">
-        <v>ADRIAN CRUZ MARTIN</v>
+        <v>GERMAN MALLO FAURE</v>
       </c>
       <c r="D80">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="E80" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F80" t="str">
-        <v>00:01:04.17</v>
+        <v>00:01:03.94</v>
       </c>
       <c r="G80">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="H80" s="1">
-        <v>45683.99949074074</v>
+        <v>44976.99949074074</v>
       </c>
       <c r="I80" t="str">
         <v>Deportista</v>
@@ -3914,7 +3914,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L80" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
       </c>
       <c r="M80" t="str">
         <v>Elche</v>
@@ -3925,28 +3925,28 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B81" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C81" t="str">
-        <v>MARCOS ESCOBEDO IRURETA</v>
+        <v>GONZALO YUSTE TRUJILLO</v>
       </c>
       <c r="D81">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="E81" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F81" t="str">
-        <v>00:01:04.30</v>
+        <v>00:01:04.16</v>
       </c>
       <c r="G81">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H81" s="1">
-        <v>45802.99949074074</v>
+        <v>45711.99949074074</v>
       </c>
       <c r="I81" t="str">
         <v>Deportista</v>
@@ -3958,24 +3958,24 @@
         <v>Electrónico</v>
       </c>
       <c r="L81" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M81" t="str">
-        <v>Castellón</v>
+        <v>ELCHE</v>
       </c>
       <c r="N81" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B82" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C82" t="str">
-        <v>KYRYLO SILVESTROV</v>
+        <v>ADRIAN CRUZ MARTIN</v>
       </c>
       <c r="D82">
         <v>2009</v>
@@ -3984,13 +3984,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F82" t="str">
-        <v>00:01:04.35</v>
+        <v>00:01:04.17</v>
       </c>
       <c r="G82">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="H82" s="1">
-        <v>45347.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I82" t="str">
         <v>Deportista</v>
@@ -4002,7 +4002,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L82" t="str">
-        <v>Autonomico Infantil de Invierno 2024</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M82" t="str">
         <v>Elche</v>
@@ -4013,28 +4013,28 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B83" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C83" t="str">
-        <v>HECTOR ALFARO OROZCO</v>
+        <v>MARCOS ESCOBEDO IRURETA</v>
       </c>
       <c r="D83">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="E83" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F83" t="str">
-        <v>00:01:04.84</v>
+        <v>00:01:04.30</v>
       </c>
       <c r="G83">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="H83" s="1">
-        <v>44709.99949074074</v>
+        <v>45802.99949074074</v>
       </c>
       <c r="I83" t="str">
         <v>Deportista</v>
@@ -4043,27 +4043,27 @@
         <v>50m</v>
       </c>
       <c r="K83" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L83" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M83" t="str">
-        <v>Sedavi</v>
+        <v>Castellón</v>
       </c>
       <c r="N83" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B84" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C84" t="str">
-        <v>DAVID MUÑOZ CEBOLLA</v>
+        <v>KYRYLO SILVESTROV</v>
       </c>
       <c r="D84">
         <v>2009</v>
@@ -4072,10 +4072,10 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F84" t="str">
-        <v>00:01:04.98</v>
+        <v>00:01:04.35</v>
       </c>
       <c r="G84">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="H84" s="1">
         <v>45347.99949074074</v>
@@ -4101,28 +4101,28 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B85" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C85" t="str">
-        <v>JAVIER SANTA FRONTERA</v>
+        <v>HECTOR ALFARO OROZCO</v>
       </c>
       <c r="D85">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="E85" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F85" t="str">
-        <v>00:01:05.00</v>
+        <v>00:01:04.84</v>
       </c>
       <c r="G85">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H85" s="1">
-        <v>42925.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I85" t="str">
         <v>Deportista</v>
@@ -4131,13 +4131,13 @@
         <v>50m</v>
       </c>
       <c r="K85" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L85" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2017</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M85" t="str">
-        <v>SEDAVÍ</v>
+        <v>Sedavi</v>
       </c>
       <c r="N85" t="str">
         <v>No</v>
@@ -4145,28 +4145,28 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B86" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C86" t="str">
-        <v>ALEXIS GARCIA VALERO</v>
+        <v>DAVID MUÑOZ CEBOLLA</v>
       </c>
       <c r="D86">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="E86" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F86" t="str">
-        <v>00:01:05.15</v>
+        <v>00:01:04.98</v>
       </c>
       <c r="G86">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H86" s="1">
-        <v>46082.99949074074</v>
+        <v>45347.99949074074</v>
       </c>
       <c r="I86" t="str">
         <v>Deportista</v>
@@ -4178,10 +4178,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L86" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>Autonomico Infantil de Invierno 2024</v>
       </c>
       <c r="M86" t="str">
-        <v>CASTELLÓN</v>
+        <v>Elche</v>
       </c>
       <c r="N86" t="str">
         <v>No</v>
@@ -4189,28 +4189,28 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B87" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C87" t="str">
-        <v>ROMARIC FORQUES</v>
+        <v>JAVIER SANTA FRONTERA</v>
       </c>
       <c r="D87">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="E87" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F87" t="str">
-        <v>00:01:05.16</v>
+        <v>00:01:05.00</v>
       </c>
       <c r="G87">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H87" s="1">
-        <v>45815.99949074074</v>
+        <v>42925.99949074074</v>
       </c>
       <c r="I87" t="str">
         <v>Deportista</v>
@@ -4222,39 +4222,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L87" t="str">
-        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2017</v>
       </c>
       <c r="M87" t="str">
-        <v>Castellón</v>
+        <v>SEDAVÍ</v>
       </c>
       <c r="N87" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B88" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C88" t="str">
-        <v>SIMON MORENO RODRIGUEZ</v>
+        <v>ROMARIC FORQUES</v>
       </c>
       <c r="D88">
-        <v>2010</v>
+        <v>1999</v>
       </c>
       <c r="E88" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F88" t="str">
-        <v>00:01:05.87</v>
+        <v>00:01:05.16</v>
       </c>
       <c r="G88">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="H88" s="1">
-        <v>46173.99949074074</v>
+        <v>45815.99949074074</v>
       </c>
       <c r="I88" t="str">
         <v>Deportista</v>
@@ -4263,39 +4263,39 @@
         <v>50m</v>
       </c>
       <c r="K88" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L88" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M88" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N88" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B89" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C89" t="str">
-        <v>HUGO RODRIGUEZ GARCIA</v>
+        <v>SIMON MORENO RODRIGUEZ</v>
       </c>
       <c r="D89">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E89" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F89" t="str">
-        <v>00:01:06.80</v>
+        <v>00:01:05.87</v>
       </c>
       <c r="G89">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="H89" s="1">
         <v>46173.99949074074</v>
@@ -4321,28 +4321,28 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B90" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C90" t="str">
-        <v>MATEO ROJAS SUAY</v>
+        <v>HUGO RODRIGUEZ GARCIA</v>
       </c>
       <c r="D90">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="E90" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F90" t="str">
-        <v>00:01:07.56</v>
+        <v>00:01:06.21</v>
       </c>
       <c r="G90">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="H90" s="1">
-        <v>45409.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I90" t="str">
         <v>Deportista</v>
@@ -4354,39 +4354,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L90" t="str">
-        <v>TROFEO INTERNACIONAL XXVIX MEMORIAL PASCUAL ROMÁN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M90" t="str">
-        <v>Elche</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N90" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B91" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C91" t="str">
-        <v>JORDI SOLERA PAREDES</v>
+        <v>MATEO ROJAS SUAY</v>
       </c>
       <c r="D91">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="E91" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F91" t="str">
-        <v>00:01:07.58</v>
+        <v>00:01:07.56</v>
       </c>
       <c r="G91">
         <v>324</v>
       </c>
       <c r="H91" s="1">
-        <v>45801.99949074074</v>
+        <v>45409.99949074074</v>
       </c>
       <c r="I91" t="str">
         <v>Deportista</v>
@@ -4398,10 +4398,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L91" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>TROFEO INTERNACIONAL XXVIX MEMORIAL PASCUAL ROMÁN</v>
       </c>
       <c r="M91" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N91" t="str">
         <v>Sí</v>
@@ -4409,28 +4409,28 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B92" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C92" t="str">
-        <v>IKER BARTOLIN GIMENEZ</v>
+        <v>JORDI SOLERA PAREDES</v>
       </c>
       <c r="D92">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="E92" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F92" t="str">
-        <v>00:01:08.12</v>
+        <v>00:01:07.58</v>
       </c>
       <c r="G92">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="H92" s="1">
-        <v>46172.99949074074</v>
+        <v>45801.99949074074</v>
       </c>
       <c r="I92" t="str">
         <v>Deportista</v>
@@ -4439,13 +4439,13 @@
         <v>50m</v>
       </c>
       <c r="K92" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L92" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M92" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N92" t="str">
         <v>Sí</v>
@@ -4453,28 +4453,28 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B93" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C93" t="str">
-        <v>RAFAEL ALBA TIRADO</v>
+        <v>HECTOR CARRASCO BLAZQUEZ</v>
       </c>
       <c r="D93">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="E93" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F93" t="str">
-        <v>00:01:08.47</v>
+        <v>00:01:07.63</v>
       </c>
       <c r="G93">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="H93" s="1">
-        <v>44709.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I93" t="str">
         <v>Deportista</v>
@@ -4483,13 +4483,13 @@
         <v>50m</v>
       </c>
       <c r="K93" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L93" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M93" t="str">
-        <v>Sedavi</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N93" t="str">
         <v>No</v>
@@ -4497,28 +4497,28 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B94" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C94" t="str">
-        <v>MANEL LAZARO VILANOVA</v>
+        <v>IKER BARTOLIN GIMENEZ</v>
       </c>
       <c r="D94">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="E94" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F94" t="str">
-        <v>00:01:08.78</v>
+        <v>00:01:08.12</v>
       </c>
       <c r="G94">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="H94" s="1">
-        <v>44611.99949074074</v>
+        <v>46172.99949074074</v>
       </c>
       <c r="I94" t="str">
         <v>Deportista</v>
@@ -4530,39 +4530,39 @@
         <v>Manual</v>
       </c>
       <c r="L94" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M94" t="str">
-        <v>Castellón</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N94" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B95" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C95" t="str">
-        <v>FEDERICO MANUEL HERMIDA BATTISTON</v>
+        <v>RAFAEL ALBA TIRADO</v>
       </c>
       <c r="D95">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E95" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F95" t="str">
-        <v>00:01:11.05</v>
+        <v>00:01:08.47</v>
       </c>
       <c r="G95">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="H95" s="1">
-        <v>45683.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I95" t="str">
         <v>Deportista</v>
@@ -4571,13 +4571,13 @@
         <v>50m</v>
       </c>
       <c r="K95" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L95" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M95" t="str">
-        <v>Elche</v>
+        <v>Sedavi</v>
       </c>
       <c r="N95" t="str">
         <v>No</v>
@@ -4585,28 +4585,28 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B96" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C96" t="str">
-        <v>DANIEL DIAZ GONZALEZ</v>
+        <v>MANEL LAZARO VILANOVA</v>
       </c>
       <c r="D96">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="E96" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F96" t="str">
-        <v>00:01:11.66</v>
+        <v>00:01:08.78</v>
       </c>
       <c r="G96">
-        <v>271</v>
+        <v>307</v>
       </c>
       <c r="H96" s="1">
-        <v>46173.99949074074</v>
+        <v>44611.99949074074</v>
       </c>
       <c r="I96" t="str">
         <v>Deportista</v>
@@ -4618,10 +4618,10 @@
         <v>Manual</v>
       </c>
       <c r="L96" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M96" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N96" t="str">
         <v>No</v>
@@ -4629,25 +4629,25 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B97" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C97" t="str">
-        <v>MARCOS RODRIGUEZ SERVER</v>
+        <v>FEDERICO MANUEL HERMIDA BATTISTON</v>
       </c>
       <c r="D97">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E97" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F97" t="str">
-        <v>00:01:12.95</v>
+        <v>00:01:11.05</v>
       </c>
       <c r="G97">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="H97" s="1">
         <v>45683.99949074074</v>
@@ -4673,28 +4673,28 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B98" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C98" t="str">
-        <v>VICTOR ROSELLO VALERA</v>
+        <v>DANIEL DIAZ GONZALEZ</v>
       </c>
       <c r="D98">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="E98" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F98" t="str">
-        <v>00:01:14.62</v>
+        <v>00:01:11.66</v>
       </c>
       <c r="G98">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H98" s="1">
-        <v>44612.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I98" t="str">
         <v>Deportista</v>
@@ -4706,39 +4706,39 @@
         <v>Manual</v>
       </c>
       <c r="L98" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M98" t="str">
-        <v>Castellón</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N98" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B99" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C99" t="str">
-        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
+        <v>MARCOS RODRIGUEZ SERVER</v>
       </c>
       <c r="D99">
-        <v>2000</v>
+        <v>2011</v>
       </c>
       <c r="E99" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F99" t="str">
-        <v>00:01:14.87</v>
+        <v>00:01:12.95</v>
       </c>
       <c r="G99">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="H99" s="1">
-        <v>42385.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I99" t="str">
         <v>Deportista</v>
@@ -4747,42 +4747,42 @@
         <v>50m</v>
       </c>
       <c r="K99" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="L99">
-        <v>201611612001</v>
+        <v>Electrónico</v>
+      </c>
+      <c r="L99" t="str">
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M99" t="str">
-        <v>CASTELLON</v>
+        <v>Elche</v>
       </c>
       <c r="N99" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B100" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C100" t="str">
-        <v>ROGER MASCARELL CARRILLO DE ALBORNOZ</v>
+        <v>VICTOR ROSELLO VALERA</v>
       </c>
       <c r="D100">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="E100" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F100" t="str">
-        <v>00:01:14.91</v>
+        <v>00:01:14.62</v>
       </c>
       <c r="G100">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H100" s="1">
-        <v>46173.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I100" t="str">
         <v>Deportista</v>
@@ -4794,39 +4794,39 @@
         <v>Manual</v>
       </c>
       <c r="L100" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M100" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N100" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B101" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C101" t="str">
-        <v>RAUL VILA ALMAZORA</v>
+        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
       </c>
       <c r="D101">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="E101" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F101" t="str">
-        <v>00:01:18.14</v>
+        <v>00:01:14.87</v>
       </c>
       <c r="G101">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="H101" s="1">
-        <v>43638.99949074074</v>
+        <v>42385.99949074074</v>
       </c>
       <c r="I101" t="str">
         <v>Deportista</v>
@@ -4837,11 +4837,11 @@
       <c r="K101" t="str">
         <v>Manual</v>
       </c>
-      <c r="L101" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+      <c r="L101">
+        <v>201611612001</v>
       </c>
       <c r="M101" t="str">
-        <v>Moncada</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N101" t="str">
         <v>Sí</v>
@@ -4849,28 +4849,28 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B102" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C102" t="str">
-        <v>RAUL MARTINEZ PAVON</v>
+        <v>ROGER MASCARELL CARRILLO DE ALBORNOZ</v>
       </c>
       <c r="D102">
-        <v>2001</v>
+        <v>2012</v>
       </c>
       <c r="E102" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F102" t="str">
-        <v>00:01:18.18</v>
+        <v>00:01:14.91</v>
       </c>
       <c r="G102">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="H102" s="1">
-        <v>43638.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I102" t="str">
         <v>Deportista</v>
@@ -4882,39 +4882,39 @@
         <v>Manual</v>
       </c>
       <c r="L102" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M102" t="str">
-        <v>Moncada</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N102" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B103" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C103" t="str">
-        <v>ADRIAN GARCIA GAZQUEZ</v>
+        <v>RAUL VILA ALMAZORA</v>
       </c>
       <c r="D103">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="E103" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F103" t="str">
-        <v>00:01:24.45</v>
+        <v>00:01:18.14</v>
       </c>
       <c r="G103">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="H103" s="1">
-        <v>42385.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I103" t="str">
         <v>Deportista</v>
@@ -4925,40 +4925,40 @@
       <c r="K103" t="str">
         <v>Manual</v>
       </c>
-      <c r="L103">
-        <v>201611612001</v>
+      <c r="L103" t="str">
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M103" t="str">
-        <v>CASTELLON</v>
+        <v>Moncada</v>
       </c>
       <c r="N103" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B104" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C104" t="str">
-        <v>LUCAS RENAU SANCHIS</v>
+        <v>RAUL MARTINEZ PAVON</v>
       </c>
       <c r="D104">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="E104" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F104" t="str">
-        <v>00:01:26.25</v>
+        <v>00:01:18.18</v>
       </c>
       <c r="G104">
-        <v>156</v>
+        <v>209</v>
       </c>
       <c r="H104" s="1">
-        <v>44612.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I104" t="str">
         <v>Deportista</v>
@@ -4970,10 +4970,10 @@
         <v>Manual</v>
       </c>
       <c r="L104" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M104" t="str">
-        <v>Castellón</v>
+        <v>Moncada</v>
       </c>
       <c r="N104" t="str">
         <v>Sí</v>
@@ -4981,28 +4981,28 @@
     </row>
     <row r="105">
       <c r="A105">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B105" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C105" t="str">
-        <v>JAVIER GARCIA ROSELLO</v>
+        <v>ADRIAN GARCIA GAZQUEZ</v>
       </c>
       <c r="D105">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="E105" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F105" t="str">
-        <v>00:01:27.44</v>
+        <v>00:01:24.45</v>
       </c>
       <c r="G105">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="H105" s="1">
-        <v>44612.99949074074</v>
+        <v>42385.99949074074</v>
       </c>
       <c r="I105" t="str">
         <v>Deportista</v>
@@ -5013,25 +5013,25 @@
       <c r="K105" t="str">
         <v>Manual</v>
       </c>
-      <c r="L105" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+      <c r="L105">
+        <v>201611612001</v>
       </c>
       <c r="M105" t="str">
-        <v>Castellón</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N105" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B106" t="str">
         <v>100 Libre</v>
       </c>
       <c r="C106" t="str">
-        <v>DENNIS BARTOLIN GIMENEZ</v>
+        <v>LUCAS RENAU SANCHIS</v>
       </c>
       <c r="D106">
         <v>2007</v>
@@ -5040,13 +5040,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F106" t="str">
-        <v>00:01:42.30</v>
+        <v>00:01:26.25</v>
       </c>
       <c r="G106">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="H106" s="1">
-        <v>44709.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I106" t="str">
         <v>Deportista</v>
@@ -5058,10 +5058,10 @@
         <v>Manual</v>
       </c>
       <c r="L106" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M106" t="str">
-        <v>Sedavi</v>
+        <v>Castellón</v>
       </c>
       <c r="N106" t="str">
         <v>Sí</v>
@@ -5069,28 +5069,28 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="B107" t="str">
-        <v>200 Libre</v>
+        <v>100 Libre</v>
       </c>
       <c r="C107" t="str">
-        <v>CARLOS MENDEZ SALVADOR</v>
+        <v>JAVIER GARCIA ROSELLO</v>
       </c>
       <c r="D107">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="E107" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F107" t="str">
-        <v>00:02:06.78</v>
+        <v>00:01:27.44</v>
       </c>
       <c r="G107">
-        <v>521</v>
+        <v>149</v>
       </c>
       <c r="H107" s="1">
-        <v>46075.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I107" t="str">
         <v>Deportista</v>
@@ -5099,13 +5099,13 @@
         <v>50m</v>
       </c>
       <c r="K107" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L107" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M107" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N107" t="str">
         <v>Sí</v>
@@ -5113,13 +5113,13 @@
     </row>
     <row r="108">
       <c r="A108">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B108" t="str">
-        <v>200 Libre</v>
+        <v>100 Libre</v>
       </c>
       <c r="C108" t="str">
-        <v>TYMOFII VLASENKO</v>
+        <v>DENNIS BARTOLIN GIMENEZ</v>
       </c>
       <c r="D108">
         <v>2007</v>
@@ -5128,13 +5128,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F108" t="str">
-        <v>00:02:07.94</v>
+        <v>00:01:42.30</v>
       </c>
       <c r="G108">
-        <v>507</v>
+        <v>93</v>
       </c>
       <c r="H108" s="1">
-        <v>44608.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I108" t="str">
         <v>Deportista</v>
@@ -5143,42 +5143,42 @@
         <v>50m</v>
       </c>
       <c r="K108" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L108" t="str">
-        <v>CAMPEONATO DE NATACION ENTRE JOVEENS Y JUNIORS</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M108" t="str">
-        <v>DNIPRO (UCRANIA)</v>
+        <v>Sedavi</v>
       </c>
       <c r="N108" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B109" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C109" t="str">
-        <v>ALVARO TERUEL BELLOCH</v>
+        <v>CARLOS MENDEZ SALVADOR</v>
       </c>
       <c r="D109">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E109" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F109" t="str">
-        <v>00:02:10.06</v>
+        <v>00:02:06.78</v>
       </c>
       <c r="G109">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="H109" s="1">
-        <v>45802.99949074074</v>
+        <v>46075.99949074074</v>
       </c>
       <c r="I109" t="str">
         <v>Deportista</v>
@@ -5190,39 +5190,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L109" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
       </c>
       <c r="M109" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N109" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B110" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C110" t="str">
-        <v>MIGUEL BAIXAULI MUÑOZ</v>
+        <v>TYMOFII VLASENKO</v>
       </c>
       <c r="D110">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="E110" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F110" t="str">
-        <v>00:02:10.38</v>
+        <v>00:02:07.94</v>
       </c>
       <c r="G110">
-        <v>479</v>
+        <v>507</v>
       </c>
       <c r="H110" s="1">
-        <v>44744.99949074074</v>
+        <v>44608.99949074074</v>
       </c>
       <c r="I110" t="str">
         <v>Deportista</v>
@@ -5234,10 +5234,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L110" t="str">
-        <v>Campeonato Autonómico Jr y Abs de Verano OPEN P50</v>
+        <v>CAMPEONATO DE NATACION ENTRE JOVEENS Y JUNIORS</v>
       </c>
       <c r="M110" t="str">
-        <v>Castellón</v>
+        <v>DNIPRO (UCRANIA)</v>
       </c>
       <c r="N110" t="str">
         <v>No</v>
@@ -5245,28 +5245,28 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B111" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C111" t="str">
-        <v>ENRIQUE GALLIFA TRONCH</v>
+        <v>ALVARO TERUEL BELLOCH</v>
       </c>
       <c r="D111">
-        <v>2001</v>
+        <v>2009</v>
       </c>
       <c r="E111" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F111" t="str">
-        <v>00:02:10.91</v>
+        <v>00:02:10.06</v>
       </c>
       <c r="G111">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="H111" s="1">
-        <v>46046.99949074074</v>
+        <v>45802.99949074074</v>
       </c>
       <c r="I111" t="str">
         <v>Deportista</v>
@@ -5278,10 +5278,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L111" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M111" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N111" t="str">
         <v>No</v>
@@ -5289,28 +5289,28 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B112" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C112" t="str">
-        <v>JAUME MORENO ROMERO</v>
+        <v>MIGUEL BAIXAULI MUÑOZ</v>
       </c>
       <c r="D112">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="E112" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F112" t="str">
-        <v>00:02:12.14</v>
+        <v>00:02:10.38</v>
       </c>
       <c r="G112">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="H112" s="1">
-        <v>45837.99949074074</v>
+        <v>44744.99949074074</v>
       </c>
       <c r="I112" t="str">
         <v>Deportista</v>
@@ -5322,7 +5322,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L112" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
+        <v>Campeonato Autonómico Jr y Abs de Verano OPEN P50</v>
       </c>
       <c r="M112" t="str">
         <v>Castellón</v>
@@ -5333,28 +5333,28 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B113" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C113" t="str">
-        <v>MARCOS ESCOBEDO IRURETA</v>
+        <v>ENRIQUE GALLIFA TRONCH</v>
       </c>
       <c r="D113">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="E113" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F113" t="str">
-        <v>00:02:14.03</v>
+        <v>00:02:10.91</v>
       </c>
       <c r="G113">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="H113" s="1">
-        <v>45802.99949074074</v>
+        <v>46046.99949074074</v>
       </c>
       <c r="I113" t="str">
         <v>Deportista</v>
@@ -5366,39 +5366,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L113" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M113" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N113" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B114" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C114" t="str">
-        <v>ALEJANDRO FABIA NOGUERA</v>
+        <v>JAUME MORENO ROMERO</v>
       </c>
       <c r="D114">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E114" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F114" t="str">
-        <v>00:02:14.16</v>
+        <v>00:02:12.14</v>
       </c>
       <c r="G114">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="H114" s="1">
-        <v>46082.99949074074</v>
+        <v>45837.99949074074</v>
       </c>
       <c r="I114" t="str">
         <v>Deportista</v>
@@ -5410,39 +5410,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L114" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
       </c>
       <c r="M114" t="str">
-        <v>CASTELLÓN</v>
+        <v>Castellón</v>
       </c>
       <c r="N114" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B115" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C115" t="str">
-        <v>ROMARIC FORQUES</v>
+        <v>ALEJANDRO FABIA NOGUERA</v>
       </c>
       <c r="D115">
-        <v>1999</v>
+        <v>2012</v>
       </c>
       <c r="E115" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F115" t="str">
-        <v>00:02:14.74</v>
+        <v>00:02:13.00</v>
       </c>
       <c r="G115">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="H115" s="1">
-        <v>45815.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I115" t="str">
         <v>Deportista</v>
@@ -5454,39 +5454,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L115" t="str">
-        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M115" t="str">
-        <v>Castellón</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N115" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B116" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C116" t="str">
-        <v>MARTIN FABIA NOGUERA</v>
+        <v>MARCOS ESCOBEDO IRURETA</v>
       </c>
       <c r="D116">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E116" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F116" t="str">
-        <v>00:02:19.28</v>
+        <v>00:02:14.03</v>
       </c>
       <c r="G116">
-        <v>393</v>
+        <v>441</v>
       </c>
       <c r="H116" s="1">
-        <v>44612.99949074074</v>
+        <v>45802.99949074074</v>
       </c>
       <c r="I116" t="str">
         <v>Deportista</v>
@@ -5495,42 +5495,42 @@
         <v>50m</v>
       </c>
       <c r="K116" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L116" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M116" t="str">
         <v>Castellón</v>
       </c>
       <c r="N116" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B117" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C117" t="str">
-        <v>MATEO ROJAS SUAY</v>
+        <v>ROMARIC FORQUES</v>
       </c>
       <c r="D117">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="E117" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F117" t="str">
-        <v>00:02:19.52</v>
+        <v>00:02:14.74</v>
       </c>
       <c r="G117">
-        <v>391</v>
+        <v>434</v>
       </c>
       <c r="H117" s="1">
-        <v>45409.99949074074</v>
+        <v>45815.99949074074</v>
       </c>
       <c r="I117" t="str">
         <v>Deportista</v>
@@ -5542,39 +5542,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L117" t="str">
-        <v>TROFEO INTERNACIONAL XXVIX MEMORIAL PASCUAL ROMÁN</v>
+        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M117" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N117" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B118" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C118" t="str">
-        <v>ARTUR SAIENKO</v>
+        <v>MARTIN FABIA NOGUERA</v>
       </c>
       <c r="D118">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="E118" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F118" t="str">
-        <v>00:02:21.25</v>
+        <v>00:02:19.28</v>
       </c>
       <c r="G118">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="H118" s="1">
-        <v>45682.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I118" t="str">
         <v>Deportista</v>
@@ -5583,13 +5583,13 @@
         <v>50m</v>
       </c>
       <c r="K118" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L118" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M118" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N118" t="str">
         <v>No</v>
@@ -5597,13 +5597,13 @@
     </row>
     <row r="119">
       <c r="A119">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B119" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C119" t="str">
-        <v>DAVID HERREROS COLL</v>
+        <v>MATEO ROJAS SUAY</v>
       </c>
       <c r="D119">
         <v>2007</v>
@@ -5612,13 +5612,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F119" t="str">
-        <v>00:02:21.45</v>
+        <v>00:02:19.52</v>
       </c>
       <c r="G119">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="H119" s="1">
-        <v>45682.99949074074</v>
+        <v>45409.99949074074</v>
       </c>
       <c r="I119" t="str">
         <v>Deportista</v>
@@ -5630,7 +5630,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L119" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>TROFEO INTERNACIONAL XXVIX MEMORIAL PASCUAL ROMÁN</v>
       </c>
       <c r="M119" t="str">
         <v>Elche</v>
@@ -5641,13 +5641,13 @@
     </row>
     <row r="120">
       <c r="A120">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B120" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C120" t="str">
-        <v>ADRIAN CRUZ MARTIN</v>
+        <v>ARTUR SAIENKO</v>
       </c>
       <c r="D120">
         <v>2009</v>
@@ -5656,10 +5656,10 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F120" t="str">
-        <v>00:02:21.50</v>
+        <v>00:02:21.25</v>
       </c>
       <c r="G120">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H120" s="1">
         <v>45682.99949074074</v>
@@ -5685,28 +5685,28 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B121" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C121" t="str">
-        <v>ADAM AMZIL IJRRARE</v>
+        <v>DAVID HERREROS COLL</v>
       </c>
       <c r="D121">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="E121" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F121" t="str">
-        <v>00:02:21.58</v>
+        <v>00:02:21.45</v>
       </c>
       <c r="G121">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H121" s="1">
-        <v>46173.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I121" t="str">
         <v>Deportista</v>
@@ -5715,13 +5715,13 @@
         <v>50m</v>
       </c>
       <c r="K121" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L121" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M121" t="str">
-        <v>Vila-Real</v>
+        <v>Elche</v>
       </c>
       <c r="N121" t="str">
         <v>No</v>
@@ -5729,28 +5729,28 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B122" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C122" t="str">
-        <v>JORDI SOLERA PAREDES</v>
+        <v>ADRIAN CRUZ MARTIN</v>
       </c>
       <c r="D122">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E122" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F122" t="str">
-        <v>00:02:22.07</v>
+        <v>00:02:21.50</v>
       </c>
       <c r="G122">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H122" s="1">
-        <v>45801.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I122" t="str">
         <v>Deportista</v>
@@ -5762,24 +5762,24 @@
         <v>Electrónico</v>
       </c>
       <c r="L122" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M122" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N122" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B123" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C123" t="str">
-        <v>DAVID MUÑOZ CEBOLLA</v>
+        <v>ADAM AMZIL IJRRARE</v>
       </c>
       <c r="D123">
         <v>2009</v>
@@ -5788,13 +5788,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F123" t="str">
-        <v>00:02:22.69</v>
+        <v>00:02:21.58</v>
       </c>
       <c r="G123">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="H123" s="1">
-        <v>45473.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I123" t="str">
         <v>Deportista</v>
@@ -5803,13 +5803,13 @@
         <v>50m</v>
       </c>
       <c r="K123" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L123" t="str">
-        <v>Autonomico Infantil de Verano</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M123" t="str">
-        <v>Sedavi(Valencia)</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N123" t="str">
         <v>No</v>
@@ -5817,28 +5817,28 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B124" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C124" t="str">
-        <v>JUAN CAMACHO MARTINEZ</v>
+        <v>JORDI SOLERA PAREDES</v>
       </c>
       <c r="D124">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="E124" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F124" t="str">
-        <v>00:02:23.13</v>
+        <v>00:02:22.07</v>
       </c>
       <c r="G124">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="H124" s="1">
-        <v>45682.99949074074</v>
+        <v>45801.99949074074</v>
       </c>
       <c r="I124" t="str">
         <v>Deportista</v>
@@ -5850,39 +5850,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L124" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M124" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N124" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B125" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C125" t="str">
-        <v>GERMAN MALLO FAURE</v>
+        <v>DAVID MUÑOZ CEBOLLA</v>
       </c>
       <c r="D125">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="E125" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F125" t="str">
-        <v>00:02:23.24</v>
+        <v>00:02:22.69</v>
       </c>
       <c r="G125">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H125" s="1">
-        <v>45095.99949074074</v>
+        <v>45473.99949074074</v>
       </c>
       <c r="I125" t="str">
         <v>Deportista</v>
@@ -5894,10 +5894,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L125" t="str">
-        <v>I Trofeo Federación 226ERS piscina 50m</v>
+        <v>Autonomico Infantil de Verano</v>
       </c>
       <c r="M125" t="str">
-        <v>Castellón</v>
+        <v>Sedavi(Valencia)</v>
       </c>
       <c r="N125" t="str">
         <v>No</v>
@@ -5905,28 +5905,28 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B126" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C126" t="str">
-        <v>GONZALO YUSTE TRUJILLO</v>
+        <v>CESAR ARROYO PEREZ</v>
       </c>
       <c r="D126">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E126" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F126" t="str">
-        <v>00:02:23.84</v>
+        <v>00:02:22.72</v>
       </c>
       <c r="G126">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="H126" s="1">
-        <v>45711.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I126" t="str">
         <v>Deportista</v>
@@ -5938,36 +5938,36 @@
         <v>Electrónico</v>
       </c>
       <c r="L126" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M126" t="str">
-        <v>ELCHE</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N126" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="127">
       <c r="A127">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B127" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C127" t="str">
-        <v>NEIZAN DE LUCA RUBIO</v>
+        <v>JUAN CAMACHO MARTINEZ</v>
       </c>
       <c r="D127">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E127" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F127" t="str">
-        <v>00:02:24.06</v>
+        <v>00:02:23.13</v>
       </c>
       <c r="G127">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="H127" s="1">
         <v>45682.99949074074</v>
@@ -5993,28 +5993,28 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B128" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C128" t="str">
-        <v>DANIEL FERNANDEZ CARO</v>
+        <v>GERMAN MALLO FAURE</v>
       </c>
       <c r="D128">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E128" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F128" t="str">
-        <v>00:02:24.74</v>
+        <v>00:02:23.24</v>
       </c>
       <c r="G128">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="H128" s="1">
-        <v>45682.99949074074</v>
+        <v>45095.99949074074</v>
       </c>
       <c r="I128" t="str">
         <v>Deportista</v>
@@ -6026,10 +6026,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L128" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>I Trofeo Federación 226ERS piscina 50m</v>
       </c>
       <c r="M128" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N128" t="str">
         <v>No</v>
@@ -6037,13 +6037,13 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B129" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C129" t="str">
-        <v>IKER BARTOLIN GIMENEZ</v>
+        <v>GONZALO YUSTE TRUJILLO</v>
       </c>
       <c r="D129">
         <v>2010</v>
@@ -6052,13 +6052,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F129" t="str">
-        <v>00:02:25.06</v>
+        <v>00:02:23.84</v>
       </c>
       <c r="G129">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="H129" s="1">
-        <v>46172.99949074074</v>
+        <v>45711.99949074074</v>
       </c>
       <c r="I129" t="str">
         <v>Deportista</v>
@@ -6067,42 +6067,42 @@
         <v>50m</v>
       </c>
       <c r="K129" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L129" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M129" t="str">
-        <v>Vila-Real</v>
+        <v>ELCHE</v>
       </c>
       <c r="N129" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B130" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C130" t="str">
-        <v>DAVID SIENRA BUGS</v>
+        <v>NEIZAN DE LUCA RUBIO</v>
       </c>
       <c r="D130">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="E130" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F130" t="str">
-        <v>00:02:25.46</v>
+        <v>00:02:24.06</v>
       </c>
       <c r="G130">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="H130" s="1">
-        <v>43632.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I130" t="str">
         <v>Deportista</v>
@@ -6114,10 +6114,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L130" t="str">
-        <v>VIII Trofeo Real Club Natación Delfín-Control Calendario Único</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M130" t="str">
-        <v>Valencia</v>
+        <v>Elche</v>
       </c>
       <c r="N130" t="str">
         <v>No</v>
@@ -6125,28 +6125,28 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B131" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C131" t="str">
-        <v>SIMON MORENO RODRIGUEZ</v>
+        <v>DANIEL FERNANDEZ CARO</v>
       </c>
       <c r="D131">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="E131" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F131" t="str">
-        <v>00:02:25.49</v>
+        <v>00:02:24.74</v>
       </c>
       <c r="G131">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="H131" s="1">
-        <v>46173.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I131" t="str">
         <v>Deportista</v>
@@ -6155,13 +6155,13 @@
         <v>50m</v>
       </c>
       <c r="K131" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L131" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M131" t="str">
-        <v>Vila-Real</v>
+        <v>Elche</v>
       </c>
       <c r="N131" t="str">
         <v>No</v>
@@ -6169,28 +6169,28 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B132" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C132" t="str">
-        <v>RAFAEL ALBA TIRADO</v>
+        <v>IKER BARTOLIN GIMENEZ</v>
       </c>
       <c r="D132">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="E132" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F132" t="str">
-        <v>00:02:26.05</v>
+        <v>00:02:25.06</v>
       </c>
       <c r="G132">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="H132" s="1">
-        <v>45108.99949074074</v>
+        <v>46172.99949074074</v>
       </c>
       <c r="I132" t="str">
         <v>Deportista</v>
@@ -6199,27 +6199,27 @@
         <v>50m</v>
       </c>
       <c r="K132" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L132" t="str">
-        <v>Campeonato Autonomico Infantil de Verano</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M132" t="str">
-        <v>ELDA</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N132" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B133" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C133" t="str">
-        <v>FLAVIUS MUSCALU</v>
+        <v>DAVID SIENRA BUGS</v>
       </c>
       <c r="D133">
         <v>2004</v>
@@ -6228,13 +6228,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F133" t="str">
-        <v>00:02:31.74</v>
+        <v>00:02:25.46</v>
       </c>
       <c r="G133">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="H133" s="1">
-        <v>43638.99949074074</v>
+        <v>43632.99949074074</v>
       </c>
       <c r="I133" t="str">
         <v>Deportista</v>
@@ -6243,13 +6243,13 @@
         <v>50m</v>
       </c>
       <c r="K133" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L133" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>VIII Trofeo Real Club Natación Delfín-Control Calendario Único</v>
       </c>
       <c r="M133" t="str">
-        <v>Moncada</v>
+        <v>Valencia</v>
       </c>
       <c r="N133" t="str">
         <v>No</v>
@@ -6257,28 +6257,28 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B134" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C134" t="str">
-        <v>MANEL LAZARO VILANOVA</v>
+        <v>SIMON MORENO RODRIGUEZ</v>
       </c>
       <c r="D134">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="E134" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F134" t="str">
-        <v>00:02:33.85</v>
+        <v>00:02:25.49</v>
       </c>
       <c r="G134">
-        <v>291</v>
+        <v>345</v>
       </c>
       <c r="H134" s="1">
-        <v>44709.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I134" t="str">
         <v>Deportista</v>
@@ -6290,10 +6290,10 @@
         <v>Manual</v>
       </c>
       <c r="L134" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M134" t="str">
-        <v>Sedavi</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N134" t="str">
         <v>No</v>
@@ -6301,28 +6301,28 @@
     </row>
     <row r="135">
       <c r="A135">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B135" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C135" t="str">
-        <v>VICTOR ROSELLO VALERA</v>
+        <v>RAFAEL ALBA TIRADO</v>
       </c>
       <c r="D135">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="E135" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F135" t="str">
-        <v>00:02:35.22</v>
+        <v>00:02:26.05</v>
       </c>
       <c r="G135">
-        <v>284</v>
+        <v>341</v>
       </c>
       <c r="H135" s="1">
-        <v>44612.99949074074</v>
+        <v>45108.99949074074</v>
       </c>
       <c r="I135" t="str">
         <v>Deportista</v>
@@ -6331,13 +6331,13 @@
         <v>50m</v>
       </c>
       <c r="K135" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L135" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>Campeonato Autonomico Infantil de Verano</v>
       </c>
       <c r="M135" t="str">
-        <v>Castellón</v>
+        <v>ELDA</v>
       </c>
       <c r="N135" t="str">
         <v>No</v>
@@ -6345,28 +6345,28 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B136" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C136" t="str">
-        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
+        <v>FLAVIUS MUSCALU</v>
       </c>
       <c r="D136">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="E136" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F136" t="str">
-        <v>00:02:36.56</v>
+        <v>00:02:31.74</v>
       </c>
       <c r="G136">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="H136" s="1">
-        <v>42707.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I136" t="str">
         <v>Deportista</v>
@@ -6375,13 +6375,13 @@
         <v>50m</v>
       </c>
       <c r="K136" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L136" t="str">
-        <v>TROFEO CASTALIA</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M136" t="str">
-        <v>CASTELLÓN</v>
+        <v>Moncada</v>
       </c>
       <c r="N136" t="str">
         <v>No</v>
@@ -6389,25 +6389,25 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B137" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C137" t="str">
-        <v>RAUL PEREZ PEIRATS</v>
+        <v>MANEL LAZARO VILANOVA</v>
       </c>
       <c r="D137">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E137" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F137" t="str">
-        <v>00:02:38.32</v>
+        <v>00:02:33.85</v>
       </c>
       <c r="G137">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="H137" s="1">
         <v>44709.99949074074</v>
@@ -6433,28 +6433,28 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B138" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C138" t="str">
-        <v>ALEXIS GARCIA VALERO</v>
+        <v>VICTOR ROSELLO VALERA</v>
       </c>
       <c r="D138">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="E138" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F138" t="str">
-        <v>00:02:40.23</v>
+        <v>00:02:35.22</v>
       </c>
       <c r="G138">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="H138" s="1">
-        <v>45682.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I138" t="str">
         <v>Deportista</v>
@@ -6463,13 +6463,13 @@
         <v>50m</v>
       </c>
       <c r="K138" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L138" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M138" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N138" t="str">
         <v>No</v>
@@ -6477,28 +6477,28 @@
     </row>
     <row r="139">
       <c r="A139">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B139" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C139" t="str">
-        <v>RAUL MARTINEZ PAVON</v>
+        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
       </c>
       <c r="D139">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="E139" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F139" t="str">
-        <v>00:02:45.43</v>
+        <v>00:02:36.56</v>
       </c>
       <c r="G139">
-        <v>234</v>
+        <v>277</v>
       </c>
       <c r="H139" s="1">
-        <v>43638.99949074074</v>
+        <v>42707.99949074074</v>
       </c>
       <c r="I139" t="str">
         <v>Deportista</v>
@@ -6507,42 +6507,42 @@
         <v>50m</v>
       </c>
       <c r="K139" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L139" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>TROFEO CASTALIA</v>
       </c>
       <c r="M139" t="str">
-        <v>Moncada</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N139" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B140" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C140" t="str">
-        <v>RAUL VILA ALMAZORA</v>
+        <v>RAUL PEREZ PEIRATS</v>
       </c>
       <c r="D140">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="E140" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F140" t="str">
-        <v>00:02:46.04</v>
+        <v>00:02:38.32</v>
       </c>
       <c r="G140">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="H140" s="1">
-        <v>43638.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I140" t="str">
         <v>Deportista</v>
@@ -6554,39 +6554,39 @@
         <v>Manual</v>
       </c>
       <c r="L140" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M140" t="str">
-        <v>Moncada</v>
+        <v>Sedavi</v>
       </c>
       <c r="N140" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="141">
       <c r="A141">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B141" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C141" t="str">
-        <v>LUCAS RENAU SANCHIS</v>
+        <v>ALEXIS GARCIA VALERO</v>
       </c>
       <c r="D141">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="E141" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F141" t="str">
-        <v>00:03:10.26</v>
+        <v>00:02:40.23</v>
       </c>
       <c r="G141">
-        <v>154</v>
+        <v>258</v>
       </c>
       <c r="H141" s="1">
-        <v>44612.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I141" t="str">
         <v>Deportista</v>
@@ -6595,13 +6595,13 @@
         <v>50m</v>
       </c>
       <c r="K141" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L141" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M141" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N141" t="str">
         <v>No</v>
@@ -6609,28 +6609,28 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B142" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C142" t="str">
-        <v>JAVIER GARCIA ROSELLO</v>
+        <v>RAUL MARTINEZ PAVON</v>
       </c>
       <c r="D142">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="E142" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F142" t="str">
-        <v>00:03:11.98</v>
+        <v>00:02:45.43</v>
       </c>
       <c r="G142">
-        <v>150</v>
+        <v>234</v>
       </c>
       <c r="H142" s="1">
-        <v>44612.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I142" t="str">
         <v>Deportista</v>
@@ -6642,39 +6642,39 @@
         <v>Manual</v>
       </c>
       <c r="L142" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M142" t="str">
-        <v>Castellón</v>
+        <v>Moncada</v>
       </c>
       <c r="N142" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B143" t="str">
         <v>200 Libre</v>
       </c>
       <c r="C143" t="str">
-        <v>DENNIS BARTOLIN GIMENEZ</v>
+        <v>RAUL VILA ALMAZORA</v>
       </c>
       <c r="D143">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="E143" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F143" t="str">
-        <v>00:03:34.40</v>
+        <v>00:02:46.04</v>
       </c>
       <c r="G143">
-        <v>108</v>
+        <v>232</v>
       </c>
       <c r="H143" s="1">
-        <v>44612.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I143" t="str">
         <v>Deportista</v>
@@ -6686,39 +6686,39 @@
         <v>Manual</v>
       </c>
       <c r="L143" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M143" t="str">
-        <v>Castellón</v>
+        <v>Moncada</v>
       </c>
       <c r="N143" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="B144" t="str">
-        <v>400 Libre</v>
+        <v>200 Libre</v>
       </c>
       <c r="C144" t="str">
-        <v>CARLOS MENDEZ SALVADOR</v>
+        <v>LUCAS RENAU SANCHIS</v>
       </c>
       <c r="D144">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E144" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F144" t="str">
-        <v>00:04:24.60</v>
+        <v>00:03:10.26</v>
       </c>
       <c r="G144">
-        <v>575</v>
+        <v>154</v>
       </c>
       <c r="H144" s="1">
-        <v>46145.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I144" t="str">
         <v>Deportista</v>
@@ -6727,42 +6727,42 @@
         <v>50m</v>
       </c>
       <c r="K144" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L144" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M144" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>Castellón</v>
       </c>
       <c r="N144" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="145">
       <c r="A145">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="B145" t="str">
-        <v>400 Libre</v>
+        <v>200 Libre</v>
       </c>
       <c r="C145" t="str">
-        <v>ROMARIC FORQUES</v>
+        <v>JAVIER GARCIA ROSELLO</v>
       </c>
       <c r="D145">
-        <v>1999</v>
+        <v>2006</v>
       </c>
       <c r="E145" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F145" t="str">
-        <v>00:04:38.97</v>
+        <v>00:03:11.98</v>
       </c>
       <c r="G145">
-        <v>491</v>
+        <v>150</v>
       </c>
       <c r="H145" s="1">
-        <v>45815.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I145" t="str">
         <v>Deportista</v>
@@ -6771,10 +6771,10 @@
         <v>50m</v>
       </c>
       <c r="K145" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L145" t="str">
-        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M145" t="str">
         <v>Castellón</v>
@@ -6785,28 +6785,28 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="B146" t="str">
-        <v>400 Libre</v>
+        <v>200 Libre</v>
       </c>
       <c r="C146" t="str">
-        <v>ENRIQUE GALLIFA TRONCH</v>
+        <v>DENNIS BARTOLIN GIMENEZ</v>
       </c>
       <c r="D146">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="E146" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F146" t="str">
-        <v>00:04:50.23</v>
+        <v>00:03:34.40</v>
       </c>
       <c r="G146">
-        <v>436</v>
+        <v>108</v>
       </c>
       <c r="H146" s="1">
-        <v>46047.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I146" t="str">
         <v>Deportista</v>
@@ -6815,13 +6815,13 @@
         <v>50m</v>
       </c>
       <c r="K146" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L146" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M146" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N146" t="str">
         <v>No</v>
@@ -6829,28 +6829,28 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B147" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C147" t="str">
-        <v>JORDI SOLERA PAREDES</v>
+        <v>CARLOS MENDEZ SALVADOR</v>
       </c>
       <c r="D147">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="E147" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F147" t="str">
-        <v>00:04:56.09</v>
+        <v>00:04:24.60</v>
       </c>
       <c r="G147">
-        <v>411</v>
+        <v>575</v>
       </c>
       <c r="H147" s="1">
-        <v>45801.99949074074</v>
+        <v>46145.99949074074</v>
       </c>
       <c r="I147" t="str">
         <v>Deportista</v>
@@ -6862,10 +6862,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L147" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
       </c>
       <c r="M147" t="str">
-        <v>Castellón</v>
+        <v>ZARAGOZA (C)</v>
       </c>
       <c r="N147" t="str">
         <v>Sí</v>
@@ -6873,28 +6873,28 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B148" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C148" t="str">
-        <v>IKER BARTOLIN GIMENEZ</v>
+        <v>ROMARIC FORQUES</v>
       </c>
       <c r="D148">
-        <v>2010</v>
+        <v>1999</v>
       </c>
       <c r="E148" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F148" t="str">
-        <v>00:05:00.35</v>
+        <v>00:04:38.97</v>
       </c>
       <c r="G148">
-        <v>393</v>
+        <v>491</v>
       </c>
       <c r="H148" s="1">
-        <v>45711.99949074074</v>
+        <v>45815.99949074074</v>
       </c>
       <c r="I148" t="str">
         <v>Deportista</v>
@@ -6906,10 +6906,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L148" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M148" t="str">
-        <v>ELCHE</v>
+        <v>Castellón</v>
       </c>
       <c r="N148" t="str">
         <v>No</v>
@@ -6917,28 +6917,28 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B149" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C149" t="str">
-        <v>MATEO ROJAS SUAY</v>
+        <v>ENRIQUE GALLIFA TRONCH</v>
       </c>
       <c r="D149">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="E149" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F149" t="str">
-        <v>00:05:08.90</v>
+        <v>00:04:50.23</v>
       </c>
       <c r="G149">
-        <v>362</v>
+        <v>436</v>
       </c>
       <c r="H149" s="1">
-        <v>45255.99949074074</v>
+        <v>46047.99949074074</v>
       </c>
       <c r="I149" t="str">
         <v>Deportista</v>
@@ -6950,10 +6950,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L149" t="str">
-        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M149" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N149" t="str">
         <v>No</v>
@@ -6961,28 +6961,28 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B150" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C150" t="str">
-        <v>DAVID HERREROS COLL</v>
+        <v>JORDI SOLERA PAREDES</v>
       </c>
       <c r="D150">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E150" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F150" t="str">
-        <v>00:05:09.43</v>
+        <v>00:04:56.09</v>
       </c>
       <c r="G150">
-        <v>360</v>
+        <v>411</v>
       </c>
       <c r="H150" s="1">
-        <v>44611.99949074074</v>
+        <v>45801.99949074074</v>
       </c>
       <c r="I150" t="str">
         <v>Deportista</v>
@@ -6991,42 +6991,42 @@
         <v>50m</v>
       </c>
       <c r="K150" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L150" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M150" t="str">
         <v>Castellón</v>
       </c>
       <c r="N150" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B151" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C151" t="str">
-        <v>ARTUR SAIENKO</v>
+        <v>IKER BARTOLIN GIMENEZ</v>
       </c>
       <c r="D151">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E151" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F151" t="str">
-        <v>00:05:14.19</v>
+        <v>00:05:00.35</v>
       </c>
       <c r="G151">
-        <v>344</v>
+        <v>393</v>
       </c>
       <c r="H151" s="1">
-        <v>45683.99949074074</v>
+        <v>45711.99949074074</v>
       </c>
       <c r="I151" t="str">
         <v>Deportista</v>
@@ -7038,10 +7038,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L151" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M151" t="str">
-        <v>Elche</v>
+        <v>ELCHE</v>
       </c>
       <c r="N151" t="str">
         <v>No</v>
@@ -7049,28 +7049,28 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B152" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C152" t="str">
-        <v>NEIZAN DE LUCA RUBIO</v>
+        <v>MATEO ROJAS SUAY</v>
       </c>
       <c r="D152">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="E152" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F152" t="str">
-        <v>00:05:17.56</v>
+        <v>00:05:08.90</v>
       </c>
       <c r="G152">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="H152" s="1">
-        <v>45683.99949074074</v>
+        <v>45255.99949074074</v>
       </c>
       <c r="I152" t="str">
         <v>Deportista</v>
@@ -7082,10 +7082,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L152" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
       </c>
       <c r="M152" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N152" t="str">
         <v>No</v>
@@ -7093,28 +7093,28 @@
     </row>
     <row r="153">
       <c r="A153">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B153" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C153" t="str">
-        <v>RAUL MARTINEZ PAVON</v>
+        <v>DAVID HERREROS COLL</v>
       </c>
       <c r="D153">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="E153" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F153" t="str">
-        <v>00:05:36.96</v>
+        <v>00:05:09.43</v>
       </c>
       <c r="G153">
-        <v>279</v>
+        <v>360</v>
       </c>
       <c r="H153" s="1">
-        <v>43638.99949074074</v>
+        <v>44611.99949074074</v>
       </c>
       <c r="I153" t="str">
         <v>Deportista</v>
@@ -7126,10 +7126,10 @@
         <v>Manual</v>
       </c>
       <c r="L153" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M153" t="str">
-        <v>Moncada</v>
+        <v>Castellón</v>
       </c>
       <c r="N153" t="str">
         <v>No</v>
@@ -7137,28 +7137,28 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B154" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C154" t="str">
-        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
+        <v>ARTUR SAIENKO</v>
       </c>
       <c r="D154">
-        <v>2000</v>
+        <v>2009</v>
       </c>
       <c r="E154" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F154" t="str">
-        <v>00:05:37.53</v>
+        <v>00:05:14.19</v>
       </c>
       <c r="G154">
-        <v>277</v>
+        <v>344</v>
       </c>
       <c r="H154" s="1">
-        <v>42385.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I154" t="str">
         <v>Deportista</v>
@@ -7167,13 +7167,13 @@
         <v>50m</v>
       </c>
       <c r="K154" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="L154">
-        <v>201611612001</v>
+        <v>Electrónico</v>
+      </c>
+      <c r="L154" t="str">
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M154" t="str">
-        <v>CASTELLON</v>
+        <v>Elche</v>
       </c>
       <c r="N154" t="str">
         <v>No</v>
@@ -7181,28 +7181,28 @@
     </row>
     <row r="155">
       <c r="A155">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B155" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C155" t="str">
-        <v>RAUL VILA ALMAZORA</v>
+        <v>NEIZAN DE LUCA RUBIO</v>
       </c>
       <c r="D155">
-        <v>2002</v>
+        <v>2011</v>
       </c>
       <c r="E155" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F155" t="str">
-        <v>00:05:40.50</v>
+        <v>00:05:17.56</v>
       </c>
       <c r="G155">
-        <v>270</v>
+        <v>333</v>
       </c>
       <c r="H155" s="1">
-        <v>43638.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I155" t="str">
         <v>Deportista</v>
@@ -7211,13 +7211,13 @@
         <v>50m</v>
       </c>
       <c r="K155" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L155" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M155" t="str">
-        <v>Moncada</v>
+        <v>Elche</v>
       </c>
       <c r="N155" t="str">
         <v>No</v>
@@ -7225,28 +7225,28 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B156" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C156" t="str">
-        <v>RAFAEL ALBA TIRADO</v>
+        <v>RAUL MARTINEZ PAVON</v>
       </c>
       <c r="D156">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="E156" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F156" t="str">
-        <v>00:05:50.02</v>
+        <v>00:05:36.96</v>
       </c>
       <c r="G156">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="H156" s="1">
-        <v>44619.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I156" t="str">
         <v>Deportista</v>
@@ -7255,13 +7255,13 @@
         <v>50m</v>
       </c>
       <c r="K156" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L156" t="str">
-        <v>Trofeo Internacional XXVII Memorial Pascual Roman</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M156" t="str">
-        <v>Elche</v>
+        <v>Moncada</v>
       </c>
       <c r="N156" t="str">
         <v>No</v>
@@ -7269,28 +7269,28 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B157" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C157" t="str">
-        <v>FLAVIUS MUSCALU</v>
+        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
       </c>
       <c r="D157">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="E157" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F157" t="str">
-        <v>00:05:55.60</v>
+        <v>00:05:37.53</v>
       </c>
       <c r="G157">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="H157" s="1">
-        <v>43275.99949074074</v>
+        <v>42385.99949074074</v>
       </c>
       <c r="I157" t="str">
         <v>Deportista</v>
@@ -7301,11 +7301,11 @@
       <c r="K157" t="str">
         <v>Manual</v>
       </c>
-      <c r="L157" t="str">
-        <v>CONTROL INFA Y MAYORES 8ª JORNADA TODOS</v>
+      <c r="L157">
+        <v>201611612001</v>
       </c>
       <c r="M157" t="str">
-        <v>MONCADA</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N157" t="str">
         <v>No</v>
@@ -7313,28 +7313,28 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B158" t="str">
         <v>400 Libre</v>
       </c>
       <c r="C158" t="str">
-        <v>DENNIS BARTOLIN GIMENEZ</v>
+        <v>RAUL VILA ALMAZORA</v>
       </c>
       <c r="D158">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="E158" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F158" t="str">
-        <v>00:07:14.21</v>
+        <v>00:05:40.50</v>
       </c>
       <c r="G158">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="H158" s="1">
-        <v>44709.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I158" t="str">
         <v>Deportista</v>
@@ -7346,10 +7346,10 @@
         <v>Manual</v>
       </c>
       <c r="L158" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M158" t="str">
-        <v>Sedavi</v>
+        <v>Moncada</v>
       </c>
       <c r="N158" t="str">
         <v>No</v>
@@ -7357,28 +7357,28 @@
     </row>
     <row r="159">
       <c r="A159">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B159" t="str">
-        <v>800 Libre</v>
+        <v>400 Libre</v>
       </c>
       <c r="C159" t="str">
-        <v>CARLOS MENDEZ SALVADOR</v>
+        <v>RAFAEL ALBA TIRADO</v>
       </c>
       <c r="D159">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E159" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F159" t="str">
-        <v>00:08:55.03</v>
+        <v>00:05:50.02</v>
       </c>
       <c r="G159">
-        <v>603</v>
+        <v>249</v>
       </c>
       <c r="H159" s="1">
-        <v>46145.99949074074</v>
+        <v>44619.99949074074</v>
       </c>
       <c r="I159" t="str">
         <v>Deportista</v>
@@ -7390,10 +7390,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L159" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>Trofeo Internacional XXVII Memorial Pascual Roman</v>
       </c>
       <c r="M159" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>Elche</v>
       </c>
       <c r="N159" t="str">
         <v>No</v>
@@ -7401,28 +7401,28 @@
     </row>
     <row r="160">
       <c r="A160">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B160" t="str">
-        <v>800 Libre</v>
+        <v>400 Libre</v>
       </c>
       <c r="C160" t="str">
-        <v>JORDI SOLERA PAREDES</v>
+        <v>FLAVIUS MUSCALU</v>
       </c>
       <c r="D160">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="E160" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F160" t="str">
-        <v>00:10:09.11</v>
+        <v>00:05:55.60</v>
       </c>
       <c r="G160">
-        <v>409</v>
+        <v>237</v>
       </c>
       <c r="H160" s="1">
-        <v>45801.99949074074</v>
+        <v>43275.99949074074</v>
       </c>
       <c r="I160" t="str">
         <v>Deportista</v>
@@ -7431,13 +7431,13 @@
         <v>50m</v>
       </c>
       <c r="K160" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L160" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>CONTROL INFA Y MAYORES 8ª JORNADA TODOS</v>
       </c>
       <c r="M160" t="str">
-        <v>Castellón</v>
+        <v>MONCADA</v>
       </c>
       <c r="N160" t="str">
         <v>No</v>
@@ -7445,28 +7445,28 @@
     </row>
     <row r="161">
       <c r="A161">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B161" t="str">
-        <v>800 Libre</v>
+        <v>400 Libre</v>
       </c>
       <c r="C161" t="str">
-        <v>IKER BARTOLIN GIMENEZ</v>
+        <v>DENNIS BARTOLIN GIMENEZ</v>
       </c>
       <c r="D161">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E161" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F161" t="str">
-        <v>00:10:14.16</v>
+        <v>00:07:14.21</v>
       </c>
       <c r="G161">
-        <v>399</v>
+        <v>130</v>
       </c>
       <c r="H161" s="1">
-        <v>45837.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I161" t="str">
         <v>Deportista</v>
@@ -7475,13 +7475,13 @@
         <v>50m</v>
       </c>
       <c r="K161" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L161" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M161" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N161" t="str">
         <v>No</v>
@@ -7489,28 +7489,28 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B162" t="str">
         <v>800 Libre</v>
       </c>
       <c r="C162" t="str">
-        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
+        <v>CARLOS MENDEZ SALVADOR</v>
       </c>
       <c r="D162">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="E162" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F162" t="str">
-        <v>00:12:46.67</v>
+        <v>00:08:55.03</v>
       </c>
       <c r="G162">
-        <v>205</v>
+        <v>603</v>
       </c>
       <c r="H162" s="1">
-        <v>42385.99949074074</v>
+        <v>46145.99949074074</v>
       </c>
       <c r="I162" t="str">
         <v>Deportista</v>
@@ -7519,42 +7519,42 @@
         <v>50m</v>
       </c>
       <c r="K162" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="L162">
-        <v>201611612001</v>
+        <v>Electrónico</v>
+      </c>
+      <c r="L162" t="str">
+        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
       </c>
       <c r="M162" t="str">
-        <v>CASTELLON</v>
+        <v>ZARAGOZA (C)</v>
       </c>
       <c r="N162" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B163" t="str">
         <v>800 Libre</v>
       </c>
       <c r="C163" t="str">
-        <v>DENNIS BARTOLIN GIMENEZ</v>
+        <v>JORDI SOLERA PAREDES</v>
       </c>
       <c r="D163">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E163" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F163" t="str">
-        <v>00:14:32.60</v>
+        <v>00:10:09.11</v>
       </c>
       <c r="G163">
-        <v>139</v>
+        <v>409</v>
       </c>
       <c r="H163" s="1">
-        <v>44709.99949074074</v>
+        <v>45801.99949074074</v>
       </c>
       <c r="I163" t="str">
         <v>Deportista</v>
@@ -7563,13 +7563,13 @@
         <v>50m</v>
       </c>
       <c r="K163" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L163" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
       </c>
       <c r="M163" t="str">
-        <v>Sedavi</v>
+        <v>Castellón</v>
       </c>
       <c r="N163" t="str">
         <v>No</v>
@@ -7577,13 +7577,13 @@
     </row>
     <row r="164">
       <c r="A164">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B164" t="str">
-        <v>1500 Libre</v>
+        <v>800 Libre</v>
       </c>
       <c r="C164" t="str">
-        <v>CARLOS MENDEZ SALVADOR</v>
+        <v>IKER BARTOLIN GIMENEZ</v>
       </c>
       <c r="D164">
         <v>2010</v>
@@ -7592,13 +7592,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F164" t="str">
-        <v>00:17:04.87</v>
+        <v>00:10:14.16</v>
       </c>
       <c r="G164">
-        <v>613</v>
+        <v>399</v>
       </c>
       <c r="H164" s="1">
-        <v>46144.99949074074</v>
+        <v>45837.99949074074</v>
       </c>
       <c r="I164" t="str">
         <v>Deportista</v>
@@ -7610,10 +7610,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L164" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
       </c>
       <c r="M164" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>Castellón</v>
       </c>
       <c r="N164" t="str">
         <v>No</v>
@@ -7621,28 +7621,28 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B165" t="str">
-        <v>1500 Libre</v>
+        <v>800 Libre</v>
       </c>
       <c r="C165" t="str">
-        <v>JORDI SOLERA PAREDES</v>
+        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
       </c>
       <c r="D165">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="E165" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F165" t="str">
-        <v>00:19:24.92</v>
+        <v>00:12:46.67</v>
       </c>
       <c r="G165">
-        <v>418</v>
+        <v>205</v>
       </c>
       <c r="H165" s="1">
-        <v>45802.99949074074</v>
+        <v>42385.99949074074</v>
       </c>
       <c r="I165" t="str">
         <v>Deportista</v>
@@ -7651,42 +7651,42 @@
         <v>50m</v>
       </c>
       <c r="K165" t="str">
-        <v>Electrónico</v>
-      </c>
-      <c r="L165" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+        <v>Manual</v>
+      </c>
+      <c r="L165">
+        <v>201611612001</v>
       </c>
       <c r="M165" t="str">
-        <v>Castellón</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N165" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B166" t="str">
-        <v>1500 Libre</v>
+        <v>800 Libre</v>
       </c>
       <c r="C166" t="str">
-        <v>IKER BARTOLIN GIMENEZ</v>
+        <v>DENNIS BARTOLIN GIMENEZ</v>
       </c>
       <c r="D166">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E166" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F166" t="str">
-        <v>00:19:29.39</v>
+        <v>00:14:32.60</v>
       </c>
       <c r="G166">
-        <v>413</v>
+        <v>139</v>
       </c>
       <c r="H166" s="1">
-        <v>45710.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I166" t="str">
         <v>Deportista</v>
@@ -7695,13 +7695,13 @@
         <v>50m</v>
       </c>
       <c r="K166" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L166" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M166" t="str">
-        <v>ELCHE</v>
+        <v>Sedavi</v>
       </c>
       <c r="N166" t="str">
         <v>No</v>
@@ -7709,28 +7709,28 @@
     </row>
     <row r="167">
       <c r="A167">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B167" t="str">
         <v>1500 Libre</v>
       </c>
       <c r="C167" t="str">
-        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
+        <v>CARLOS MENDEZ SALVADOR</v>
       </c>
       <c r="D167">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="E167" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F167" t="str">
-        <v>00:23:38.31</v>
+        <v>00:17:04.87</v>
       </c>
       <c r="G167">
-        <v>231</v>
+        <v>613</v>
       </c>
       <c r="H167" s="1">
-        <v>42385.99949074074</v>
+        <v>46144.99949074074</v>
       </c>
       <c r="I167" t="str">
         <v>Deportista</v>
@@ -7739,13 +7739,13 @@
         <v>50m</v>
       </c>
       <c r="K167" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="L167">
-        <v>201611612001</v>
+        <v>Electrónico</v>
+      </c>
+      <c r="L167" t="str">
+        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
       </c>
       <c r="M167" t="str">
-        <v>CASTELLON</v>
+        <v>ZARAGOZA (C)</v>
       </c>
       <c r="N167" t="str">
         <v>No</v>
@@ -7753,51 +7753,183 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B168" t="str">
         <v>1500 Libre</v>
       </c>
       <c r="C168" t="str">
+        <v>JORDI SOLERA PAREDES</v>
+      </c>
+      <c r="D168">
+        <v>2008</v>
+      </c>
+      <c r="E168" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F168" t="str">
+        <v>00:19:24.92</v>
+      </c>
+      <c r="G168">
+        <v>418</v>
+      </c>
+      <c r="H168" s="1">
+        <v>45802.99949074074</v>
+      </c>
+      <c r="I168" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J168" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K168" t="str">
+        <v>Electrónico</v>
+      </c>
+      <c r="L168" t="str">
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE VERANO 2025</v>
+      </c>
+      <c r="M168" t="str">
+        <v>Castellón</v>
+      </c>
+      <c r="N168" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>3</v>
+      </c>
+      <c r="B169" t="str">
+        <v>1500 Libre</v>
+      </c>
+      <c r="C169" t="str">
+        <v>IKER BARTOLIN GIMENEZ</v>
+      </c>
+      <c r="D169">
+        <v>2010</v>
+      </c>
+      <c r="E169" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F169" t="str">
+        <v>00:19:29.39</v>
+      </c>
+      <c r="G169">
+        <v>413</v>
+      </c>
+      <c r="H169" s="1">
+        <v>45710.99949074074</v>
+      </c>
+      <c r="I169" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J169" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K169" t="str">
+        <v>Electrónico</v>
+      </c>
+      <c r="L169" t="str">
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+      </c>
+      <c r="M169" t="str">
+        <v>ELCHE</v>
+      </c>
+      <c r="N169" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>4</v>
+      </c>
+      <c r="B170" t="str">
+        <v>1500 Libre</v>
+      </c>
+      <c r="C170" t="str">
+        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
+      </c>
+      <c r="D170">
+        <v>2000</v>
+      </c>
+      <c r="E170" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F170" t="str">
+        <v>00:23:38.31</v>
+      </c>
+      <c r="G170">
+        <v>231</v>
+      </c>
+      <c r="H170" s="1">
+        <v>42385.99949074074</v>
+      </c>
+      <c r="I170" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J170" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K170" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="L170">
+        <v>201611612001</v>
+      </c>
+      <c r="M170" t="str">
+        <v>CASTELLON</v>
+      </c>
+      <c r="N170" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>5</v>
+      </c>
+      <c r="B171" t="str">
+        <v>1500 Libre</v>
+      </c>
+      <c r="C171" t="str">
         <v>DENNIS BARTOLIN GIMENEZ</v>
       </c>
-      <c r="D168">
+      <c r="D171">
         <v>2007</v>
       </c>
-      <c r="E168" t="str">
-        <v>C.N. MEDITERRANEO VALENCIA</v>
-      </c>
-      <c r="F168" t="str">
+      <c r="E171" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F171" t="str">
         <v>00:29:47.73</v>
       </c>
-      <c r="G168">
+      <c r="G171">
         <v>116</v>
       </c>
-      <c r="H168" s="1">
+      <c r="H171" s="1">
         <v>44709.99949074074</v>
       </c>
-      <c r="I168" t="str">
-        <v>Deportista</v>
-      </c>
-      <c r="J168" t="str">
-        <v>50m</v>
-      </c>
-      <c r="K168" t="str">
+      <c r="I171" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J171" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K171" t="str">
         <v>Manual</v>
       </c>
-      <c r="L168" t="str">
+      <c r="L171" t="str">
         <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
-      <c r="M168" t="str">
+      <c r="M171" t="str">
         <v>Sedavi</v>
       </c>
-      <c r="N168" t="str">
+      <c r="N171" t="str">
         <v>No</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O168"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O171"/>
   </ignoredErrors>
 </worksheet>
 </file>